--- a/data/T2_raw.xlsx
+++ b/data/T2_raw.xlsx
@@ -2016,7 +2016,7 @@
         <v>5</v>
       </c>
       <c r="M2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N2">
         <v>5</v>
@@ -2039,7 +2039,7 @@
         <v>105</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -2057,7 +2057,7 @@
         <v>4</v>
       </c>
       <c r="K3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -2415,7 +2415,7 @@
         <v>113</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -2427,7 +2427,7 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J11">
         <v>2</v>
@@ -2462,19 +2462,19 @@
         <v>114</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>2</v>
@@ -2509,19 +2509,19 @@
         <v>115</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -2565,7 +2565,7 @@
         <v>5</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>4</v>
@@ -2885,19 +2885,19 @@
         <v>123</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J21">
         <v>3</v>
@@ -2979,19 +2979,19 @@
         <v>125</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>3</v>
@@ -3026,19 +3026,19 @@
         <v>126</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -3355,19 +3355,19 @@
         <v>133</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>4</v>
@@ -3405,7 +3405,7 @@
         <v>5</v>
       </c>
       <c r="F32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G32">
         <v>5</v>
@@ -3449,16 +3449,16 @@
         <v>135</v>
       </c>
       <c r="E33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33">
         <v>5</v>
       </c>
       <c r="H33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>5</v>
@@ -3499,7 +3499,7 @@
         <v>5</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G34">
         <v>5</v>
@@ -3687,16 +3687,16 @@
         <v>5</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H38">
         <v>5</v>
       </c>
       <c r="I38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J38">
         <v>4</v>
@@ -3966,19 +3966,19 @@
         <v>146</v>
       </c>
       <c r="E44">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I44">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J44">
         <v>3</v>
@@ -4013,16 +4013,16 @@
         <v>147</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G45">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H45">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I45">
         <v>5</v>
@@ -4248,16 +4248,16 @@
         <v>152</v>
       </c>
       <c r="E50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I50">
         <v>5</v>
@@ -4404,7 +4404,7 @@
         <v>2</v>
       </c>
       <c r="J53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K53">
         <v>5</v>
@@ -4413,10 +4413,10 @@
         <v>5</v>
       </c>
       <c r="M53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N53">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O53">
         <v>6</v>
@@ -4436,16 +4436,16 @@
         <v>156</v>
       </c>
       <c r="E54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F54">
         <v>5</v>
       </c>
       <c r="G54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I54">
         <v>5</v>
@@ -4483,19 +4483,19 @@
         <v>157</v>
       </c>
       <c r="E55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F55">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G55">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H55">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I55">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J55">
         <v>3</v>
@@ -4542,7 +4542,7 @@
         <v>5</v>
       </c>
       <c r="I56">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J56">
         <v>3</v>
@@ -4583,13 +4583,13 @@
         <v>5</v>
       </c>
       <c r="G57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H57">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -4633,7 +4633,7 @@
         <v>5</v>
       </c>
       <c r="H58">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I58">
         <v>5</v>
@@ -4742,7 +4742,7 @@
         <v>4</v>
       </c>
       <c r="M60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N60">
         <v>4</v>
@@ -4859,19 +4859,19 @@
         <v>165</v>
       </c>
       <c r="E63">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J63">
         <v>3</v>
@@ -5009,7 +5009,7 @@
         <v>5</v>
       </c>
       <c r="H66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I66">
         <v>4</v>
@@ -5047,19 +5047,19 @@
         <v>169</v>
       </c>
       <c r="E67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J67">
         <v>2</v>
@@ -5438,19 +5438,19 @@
         <v>2</v>
       </c>
       <c r="J75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L75">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O75">
         <v>6</v>
@@ -5517,19 +5517,19 @@
         <v>179</v>
       </c>
       <c r="E77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F77">
         <v>5</v>
       </c>
       <c r="G77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H77">
         <v>5</v>
       </c>
       <c r="I77">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J77">
         <v>4</v>
@@ -5629,13 +5629,13 @@
         <v>5</v>
       </c>
       <c r="K79">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L79">
         <v>5</v>
       </c>
       <c r="M79">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N79">
         <v>4</v>
@@ -5658,19 +5658,19 @@
         <v>182</v>
       </c>
       <c r="E80">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H80">
         <v>5</v>
       </c>
       <c r="I80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J80">
         <v>3</v>
@@ -5711,7 +5711,7 @@
         <v>4</v>
       </c>
       <c r="G81">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H81">
         <v>4</v>
@@ -5858,7 +5858,7 @@
         <v>4</v>
       </c>
       <c r="I84">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J84">
         <v>3</v>
@@ -5990,7 +5990,7 @@
         <v>4</v>
       </c>
       <c r="F87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G87">
         <v>4</v>
@@ -6043,7 +6043,7 @@
         <v>5</v>
       </c>
       <c r="H88">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I88">
         <v>4</v>
@@ -6140,7 +6140,7 @@
         <v>4</v>
       </c>
       <c r="I90">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J90">
         <v>4</v>
@@ -6222,19 +6222,19 @@
         <v>194</v>
       </c>
       <c r="E92">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F92">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G92">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H92">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I92">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J92">
         <v>2</v>
@@ -6316,19 +6316,19 @@
         <v>196</v>
       </c>
       <c r="E94">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F94">
         <v>5</v>
       </c>
       <c r="G94">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H94">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I94">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J94">
         <v>1</v>
@@ -6410,16 +6410,16 @@
         <v>198</v>
       </c>
       <c r="E96">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F96">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G96">
         <v>5</v>
       </c>
       <c r="H96">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I96">
         <v>5</v>
@@ -6431,10 +6431,10 @@
         <v>5</v>
       </c>
       <c r="L96">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M96">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N96">
         <v>5</v>
@@ -6601,13 +6601,13 @@
         <v>5</v>
       </c>
       <c r="F100">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G100">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H100">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I100">
         <v>5</v>
@@ -6648,7 +6648,7 @@
         <v>5</v>
       </c>
       <c r="F101">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G101">
         <v>5</v>
@@ -6757,7 +6757,7 @@
         <v>4</v>
       </c>
       <c r="K103">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L103">
         <v>4</v>
@@ -6883,7 +6883,7 @@
         <v>5</v>
       </c>
       <c r="F106">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G106">
         <v>5</v>
@@ -6983,10 +6983,10 @@
         <v>5</v>
       </c>
       <c r="H108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J108">
         <v>3</v>
@@ -7068,16 +7068,16 @@
         <v>212</v>
       </c>
       <c r="E110">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F110">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G110">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H110">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I110">
         <v>5</v>
@@ -7115,10 +7115,10 @@
         <v>213</v>
       </c>
       <c r="E111">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F111">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G111">
         <v>4</v>
@@ -7162,19 +7162,19 @@
         <v>214</v>
       </c>
       <c r="E112">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F112">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G112">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H112">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I112">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J112">
         <v>4</v>
@@ -7256,7 +7256,7 @@
         <v>216</v>
       </c>
       <c r="E114">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F114">
         <v>5</v>
@@ -7306,16 +7306,16 @@
         <v>5</v>
       </c>
       <c r="F115">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G115">
         <v>5</v>
       </c>
       <c r="H115">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I115">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J115">
         <v>1</v>
@@ -7409,7 +7409,7 @@
         <v>4</v>
       </c>
       <c r="I117">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J117">
         <v>4</v>
@@ -7450,7 +7450,7 @@
         <v>5</v>
       </c>
       <c r="G118">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H118">
         <v>5</v>
@@ -7459,7 +7459,7 @@
         <v>5</v>
       </c>
       <c r="J118">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K118">
         <v>4</v>
@@ -7491,19 +7491,19 @@
         <v>221</v>
       </c>
       <c r="E119">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F119">
         <v>5</v>
       </c>
       <c r="G119">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H119">
         <v>5</v>
       </c>
       <c r="I119">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J119">
         <v>2</v>
@@ -7538,19 +7538,19 @@
         <v>222</v>
       </c>
       <c r="E120">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F120">
         <v>5</v>
       </c>
       <c r="G120">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H120">
         <v>5</v>
       </c>
       <c r="I120">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J120">
         <v>4</v>
@@ -7635,7 +7635,7 @@
         <v>5</v>
       </c>
       <c r="F122">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G122">
         <v>5</v>
@@ -7726,19 +7726,19 @@
         <v>226</v>
       </c>
       <c r="E124">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F124">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G124">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H124">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I124">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J124">
         <v>1</v>
@@ -7917,7 +7917,7 @@
         <v>4</v>
       </c>
       <c r="F128">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G128">
         <v>5</v>
@@ -8014,13 +8014,13 @@
         <v>5</v>
       </c>
       <c r="G130">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H130">
         <v>5</v>
       </c>
       <c r="I130">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J130">
         <v>3</v>
@@ -8055,19 +8055,19 @@
         <v>233</v>
       </c>
       <c r="E131">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F131">
         <v>5</v>
       </c>
       <c r="G131">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H131">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I131">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J131">
         <v>1</v>
@@ -8155,10 +8155,10 @@
         <v>4</v>
       </c>
       <c r="G133">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H133">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I133">
         <v>5</v>
@@ -8384,19 +8384,19 @@
         <v>240</v>
       </c>
       <c r="E138">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F138">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G138">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H138">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I138">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J138">
         <v>3</v>
@@ -8487,10 +8487,10 @@
         <v>5</v>
       </c>
       <c r="H140">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I140">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J140">
         <v>3</v>
@@ -8525,13 +8525,13 @@
         <v>243</v>
       </c>
       <c r="E141">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F141">
         <v>5</v>
       </c>
       <c r="G141">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H141">
         <v>5</v>
@@ -8575,7 +8575,7 @@
         <v>5</v>
       </c>
       <c r="F142">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G142">
         <v>5</v>
@@ -8666,19 +8666,19 @@
         <v>246</v>
       </c>
       <c r="E144">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F144">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G144">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H144">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I144">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J144">
         <v>1</v>
@@ -8713,16 +8713,16 @@
         <v>247</v>
       </c>
       <c r="E145">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F145">
         <v>5</v>
       </c>
       <c r="G145">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H145">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I145">
         <v>5</v>
@@ -8828,7 +8828,7 @@
         <v>4</v>
       </c>
       <c r="L147">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M147">
         <v>4</v>
@@ -9089,19 +9089,19 @@
         <v>255</v>
       </c>
       <c r="E153">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F153">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G153">
         <v>5</v>
       </c>
       <c r="H153">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I153">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J153">
         <v>2</v>
@@ -9139,7 +9139,7 @@
         <v>5</v>
       </c>
       <c r="F154">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G154">
         <v>4</v>
@@ -9204,7 +9204,7 @@
         <v>3</v>
       </c>
       <c r="L155">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M155">
         <v>5</v>
@@ -9230,19 +9230,19 @@
         <v>258</v>
       </c>
       <c r="E156">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F156">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G156">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H156">
         <v>5</v>
       </c>
       <c r="I156">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J156">
         <v>2</v>
@@ -9277,19 +9277,19 @@
         <v>259</v>
       </c>
       <c r="E157">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F157">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G157">
         <v>5</v>
       </c>
       <c r="H157">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I157">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J157">
         <v>3</v>
@@ -9465,19 +9465,19 @@
         <v>263</v>
       </c>
       <c r="E161">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F161">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G161">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H161">
         <v>5</v>
       </c>
       <c r="I161">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J161">
         <v>2</v>
@@ -9606,19 +9606,19 @@
         <v>266</v>
       </c>
       <c r="E164">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F164">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G164">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H164">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I164">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J164">
         <v>4</v>
@@ -9662,7 +9662,7 @@
         <v>5</v>
       </c>
       <c r="H165">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I165">
         <v>5</v>
@@ -9674,7 +9674,7 @@
         <v>5</v>
       </c>
       <c r="L165">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M165">
         <v>5</v>
@@ -9794,7 +9794,7 @@
         <v>270</v>
       </c>
       <c r="E168">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F168">
         <v>4</v>
@@ -9803,7 +9803,7 @@
         <v>5</v>
       </c>
       <c r="H168">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I168">
         <v>5</v>
@@ -9815,10 +9815,10 @@
         <v>4</v>
       </c>
       <c r="L168">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M168">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N168">
         <v>4</v>
@@ -9888,19 +9888,19 @@
         <v>272</v>
       </c>
       <c r="E170">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F170">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G170">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H170">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I170">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J170">
         <v>1</v>
@@ -9935,19 +9935,19 @@
         <v>273</v>
       </c>
       <c r="E171">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F171">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G171">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H171">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I171">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J171">
         <v>2</v>
@@ -10076,7 +10076,7 @@
         <v>276</v>
       </c>
       <c r="E174">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F174">
         <v>5</v>
@@ -10085,7 +10085,7 @@
         <v>5</v>
       </c>
       <c r="H174">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I174">
         <v>5</v>
@@ -10220,7 +10220,7 @@
         <v>4</v>
       </c>
       <c r="F177">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G177">
         <v>5</v>
@@ -10311,10 +10311,10 @@
         <v>281</v>
       </c>
       <c r="E179">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F179">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G179">
         <v>5</v>
@@ -10323,7 +10323,7 @@
         <v>5</v>
       </c>
       <c r="I179">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J179">
         <v>4</v>
@@ -10332,7 +10332,7 @@
         <v>3</v>
       </c>
       <c r="L179">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M179">
         <v>5</v>
@@ -10452,19 +10452,19 @@
         <v>284</v>
       </c>
       <c r="E182">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F182">
         <v>5</v>
       </c>
       <c r="G182">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H182">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I182">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J182">
         <v>1</v>
@@ -10502,10 +10502,10 @@
         <v>5</v>
       </c>
       <c r="F183">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G183">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H183">
         <v>5</v>
@@ -10593,7 +10593,7 @@
         <v>287</v>
       </c>
       <c r="E185">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F185">
         <v>4</v>
@@ -10781,19 +10781,19 @@
         <v>291</v>
       </c>
       <c r="E189">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F189">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G189">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H189">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I189">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J189">
         <v>2</v>
@@ -10922,19 +10922,19 @@
         <v>294</v>
       </c>
       <c r="E192">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F192">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G192">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H192">
         <v>5</v>
       </c>
       <c r="I192">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J192">
         <v>1</v>
@@ -11078,19 +11078,19 @@
         <v>4</v>
       </c>
       <c r="J195">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K195">
         <v>5</v>
       </c>
       <c r="L195">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M195">
         <v>5</v>
       </c>
       <c r="N195">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O195">
         <v>6</v>
@@ -11110,19 +11110,19 @@
         <v>298</v>
       </c>
       <c r="E196">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F196">
         <v>5</v>
       </c>
       <c r="G196">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H196">
         <v>5</v>
       </c>
       <c r="I196">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J196">
         <v>3</v>
@@ -11172,19 +11172,19 @@
         <v>3</v>
       </c>
       <c r="J197">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K197">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L197">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M197">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N197">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O197">
         <v>6</v>
@@ -11213,7 +11213,7 @@
         <v>5</v>
       </c>
       <c r="H198">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I198">
         <v>5</v>
@@ -11301,7 +11301,7 @@
         <v>5</v>
       </c>
       <c r="F200">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G200">
         <v>5</v>
@@ -11486,19 +11486,19 @@
         <v>306</v>
       </c>
       <c r="E204">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F204">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G204">
         <v>5</v>
       </c>
       <c r="H204">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I204">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J204">
         <v>4</v>
@@ -11545,7 +11545,7 @@
         <v>5</v>
       </c>
       <c r="I205">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J205">
         <v>2</v>
@@ -11636,7 +11636,7 @@
         <v>5</v>
       </c>
       <c r="H207">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I207">
         <v>5</v>
@@ -11865,10 +11865,10 @@
         <v>5</v>
       </c>
       <c r="F212">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G212">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H212">
         <v>5</v>
@@ -11956,19 +11956,19 @@
         <v>316</v>
       </c>
       <c r="E214">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F214">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G214">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H214">
         <v>5</v>
       </c>
       <c r="I214">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J214">
         <v>1</v>
@@ -12053,31 +12053,31 @@
         <v>5</v>
       </c>
       <c r="F216">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G216">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H216">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I216">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J216">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K216">
         <v>4</v>
       </c>
       <c r="L216">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M216">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N216">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O216">
         <v>6</v>
@@ -12100,16 +12100,16 @@
         <v>5</v>
       </c>
       <c r="F217">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G217">
         <v>5</v>
       </c>
       <c r="H217">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I217">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J217">
         <v>2</v>
@@ -12191,7 +12191,7 @@
         <v>320</v>
       </c>
       <c r="E219">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F219">
         <v>4</v>
@@ -12200,10 +12200,10 @@
         <v>5</v>
       </c>
       <c r="H219">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I219">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J219">
         <v>3</v>
@@ -12385,13 +12385,13 @@
         <v>4</v>
       </c>
       <c r="G223">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H223">
         <v>5</v>
       </c>
       <c r="I223">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J223">
         <v>2</v>
@@ -12438,7 +12438,7 @@
         <v>5</v>
       </c>
       <c r="I224">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J224">
         <v>1</v>
@@ -12576,10 +12576,10 @@
         <v>5</v>
       </c>
       <c r="H227">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I227">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J227">
         <v>3</v>
@@ -12626,7 +12626,7 @@
         <v>5</v>
       </c>
       <c r="I228">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J228">
         <v>3</v>
@@ -12673,7 +12673,7 @@
         <v>4</v>
       </c>
       <c r="I229">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J229">
         <v>2</v>
@@ -12755,19 +12755,19 @@
         <v>332</v>
       </c>
       <c r="E231">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F231">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G231">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H231">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I231">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J231">
         <v>3</v>
@@ -12943,19 +12943,19 @@
         <v>336</v>
       </c>
       <c r="E235">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F235">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G235">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H235">
         <v>5</v>
       </c>
       <c r="I235">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J235">
         <v>2</v>
@@ -12990,13 +12990,13 @@
         <v>337</v>
       </c>
       <c r="E236">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F236">
         <v>5</v>
       </c>
       <c r="G236">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H236">
         <v>5</v>
@@ -13087,10 +13087,10 @@
         <v>4</v>
       </c>
       <c r="F238">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G238">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H238">
         <v>5</v>
@@ -13131,19 +13131,19 @@
         <v>340</v>
       </c>
       <c r="E239">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F239">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G239">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H239">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I239">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J239">
         <v>3</v>
@@ -13178,19 +13178,19 @@
         <v>341</v>
       </c>
       <c r="E240">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F240">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G240">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H240">
         <v>5</v>
       </c>
       <c r="I240">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J240">
         <v>2</v>
@@ -13413,19 +13413,19 @@
         <v>346</v>
       </c>
       <c r="E245">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F245">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G245">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H245">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I245">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J245">
         <v>1</v>
@@ -13472,7 +13472,7 @@
         <v>5</v>
       </c>
       <c r="I246">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J246">
         <v>3</v>
@@ -13554,19 +13554,19 @@
         <v>349</v>
       </c>
       <c r="E248">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F248">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G248">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H248">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I248">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J248">
         <v>2</v>
@@ -13648,16 +13648,16 @@
         <v>351</v>
       </c>
       <c r="E250">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F250">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G250">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H250">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I250">
         <v>5</v>
@@ -13722,7 +13722,7 @@
         <v>4</v>
       </c>
       <c r="N251">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O251">
         <v>6</v>
@@ -13742,19 +13742,19 @@
         <v>353</v>
       </c>
       <c r="E252">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F252">
         <v>5</v>
       </c>
       <c r="G252">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H252">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I252">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J252">
         <v>3</v>
@@ -13883,10 +13883,10 @@
         <v>356</v>
       </c>
       <c r="E255">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F255">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G255">
         <v>5</v>
@@ -14024,7 +14024,7 @@
         <v>359</v>
       </c>
       <c r="E258">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F258">
         <v>5</v>
@@ -14086,19 +14086,19 @@
         <v>4</v>
       </c>
       <c r="J259">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K259">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L259">
         <v>5</v>
       </c>
       <c r="M259">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N259">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O259">
         <v>6</v>
@@ -14268,7 +14268,7 @@
         <v>5</v>
       </c>
       <c r="H263">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I263">
         <v>5</v>
@@ -14353,7 +14353,7 @@
         <v>366</v>
       </c>
       <c r="E265">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F265">
         <v>5</v>
@@ -14365,7 +14365,7 @@
         <v>5</v>
       </c>
       <c r="I265">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J265">
         <v>4</v>
@@ -14400,16 +14400,16 @@
         <v>367</v>
       </c>
       <c r="E266">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F266">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G266">
         <v>5</v>
       </c>
       <c r="H266">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I266">
         <v>5</v>
@@ -14450,10 +14450,10 @@
         <v>5</v>
       </c>
       <c r="F267">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G267">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H267">
         <v>4</v>
@@ -14515,13 +14515,13 @@
         <v>4</v>
       </c>
       <c r="L268">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M268">
         <v>5</v>
       </c>
       <c r="N268">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O268">
         <v>6</v>
@@ -14635,19 +14635,19 @@
         <v>372</v>
       </c>
       <c r="E271">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F271">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G271">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H271">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I271">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J271">
         <v>2</v>
@@ -14729,16 +14729,16 @@
         <v>374</v>
       </c>
       <c r="E273">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F273">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G273">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H273">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I273">
         <v>5</v>
@@ -14891,13 +14891,13 @@
         <v>5</v>
       </c>
       <c r="L276">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M276">
         <v>5</v>
       </c>
       <c r="N276">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O276">
         <v>6</v>
@@ -14917,19 +14917,19 @@
         <v>378</v>
       </c>
       <c r="E277">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F277">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G277">
         <v>5</v>
       </c>
       <c r="H277">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I277">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J277">
         <v>2</v>
@@ -14976,7 +14976,7 @@
         <v>5</v>
       </c>
       <c r="I278">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J278">
         <v>3</v>
@@ -15014,7 +15014,7 @@
         <v>4</v>
       </c>
       <c r="F279">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G279">
         <v>4</v>
@@ -15132,7 +15132,7 @@
         <v>4</v>
       </c>
       <c r="N281">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O281">
         <v>6</v>
@@ -15161,7 +15161,7 @@
         <v>5</v>
       </c>
       <c r="H282">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I282">
         <v>5</v>
@@ -15293,7 +15293,7 @@
         <v>384</v>
       </c>
       <c r="E285">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F285">
         <v>5</v>
@@ -15449,16 +15449,16 @@
         <v>4</v>
       </c>
       <c r="J288">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K288">
         <v>5</v>
       </c>
       <c r="L288">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M288">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N288">
         <v>5</v>
@@ -15481,7 +15481,7 @@
         <v>388</v>
       </c>
       <c r="E289">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F289">
         <v>5</v>
@@ -15719,16 +15719,16 @@
         <v>5</v>
       </c>
       <c r="F294">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G294">
         <v>5</v>
       </c>
       <c r="H294">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I294">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J294">
         <v>4</v>
@@ -15790,7 +15790,7 @@
         <v>5</v>
       </c>
       <c r="N295">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O295">
         <v>6</v>
@@ -15963,7 +15963,7 @@
         <v>5</v>
       </c>
       <c r="I299">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J299">
         <v>3</v>
@@ -15998,19 +15998,19 @@
         <v>399</v>
       </c>
       <c r="E300">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F300">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G300">
         <v>5</v>
       </c>
       <c r="H300">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I300">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J300">
         <v>3</v>
@@ -16333,10 +16333,10 @@
         <v>5</v>
       </c>
       <c r="G307">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H307">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I307">
         <v>5</v>
@@ -16468,19 +16468,19 @@
         <v>409</v>
       </c>
       <c r="E310">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F310">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G310">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H310">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I310">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J310">
         <v>3</v>
@@ -16515,16 +16515,16 @@
         <v>410</v>
       </c>
       <c r="E311">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F311">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G311">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H311">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I311">
         <v>5</v>
@@ -16618,7 +16618,7 @@
         <v>4</v>
       </c>
       <c r="H313">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I313">
         <v>5</v>
@@ -16656,13 +16656,13 @@
         <v>413</v>
       </c>
       <c r="E314">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F314">
         <v>5</v>
       </c>
       <c r="G314">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H314">
         <v>5</v>
@@ -16703,7 +16703,7 @@
         <v>414</v>
       </c>
       <c r="E315">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F315">
         <v>5</v>
@@ -16938,19 +16938,19 @@
         <v>419</v>
       </c>
       <c r="E320">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F320">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G320">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H320">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I320">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J320">
         <v>1</v>
@@ -17126,16 +17126,16 @@
         <v>423</v>
       </c>
       <c r="E324">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F324">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G324">
         <v>5</v>
       </c>
       <c r="H324">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I324">
         <v>5</v>
@@ -17226,7 +17226,7 @@
         <v>5</v>
       </c>
       <c r="G326">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H326">
         <v>5</v>
@@ -17361,19 +17361,19 @@
         <v>428</v>
       </c>
       <c r="E329">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F329">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G329">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H329">
         <v>5</v>
       </c>
       <c r="I329">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J329">
         <v>2</v>
@@ -17408,16 +17408,16 @@
         <v>429</v>
       </c>
       <c r="E330">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F330">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G330">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H330">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I330">
         <v>5</v>
@@ -17455,7 +17455,7 @@
         <v>430</v>
       </c>
       <c r="E331">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F331">
         <v>5</v>
@@ -17467,7 +17467,7 @@
         <v>5</v>
       </c>
       <c r="I331">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J331">
         <v>1</v>
@@ -17502,16 +17502,16 @@
         <v>431</v>
       </c>
       <c r="E332">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F332">
         <v>5</v>
       </c>
       <c r="G332">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H332">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I332">
         <v>5</v>
@@ -17549,19 +17549,19 @@
         <v>432</v>
       </c>
       <c r="E333">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F333">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G333">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H333">
         <v>5</v>
       </c>
       <c r="I333">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J333">
         <v>2</v>
@@ -17878,7 +17878,7 @@
         <v>439</v>
       </c>
       <c r="E340">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F340">
         <v>5</v>
@@ -17928,7 +17928,7 @@
         <v>4</v>
       </c>
       <c r="F341">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G341">
         <v>5</v>
@@ -17972,19 +17972,19 @@
         <v>441</v>
       </c>
       <c r="E342">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F342">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G342">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H342">
         <v>5</v>
       </c>
       <c r="I342">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J342">
         <v>3</v>
@@ -18113,19 +18113,19 @@
         <v>444</v>
       </c>
       <c r="E345">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F345">
         <v>5</v>
       </c>
       <c r="G345">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H345">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I345">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J345">
         <v>4</v>
@@ -18254,19 +18254,19 @@
         <v>447</v>
       </c>
       <c r="E348">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F348">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G348">
         <v>4</v>
       </c>
       <c r="H348">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I348">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J348">
         <v>1</v>
@@ -18495,7 +18495,7 @@
         <v>5</v>
       </c>
       <c r="G353">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H353">
         <v>5</v>
@@ -18536,7 +18536,7 @@
         <v>453</v>
       </c>
       <c r="E354">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F354">
         <v>4</v>
@@ -18545,7 +18545,7 @@
         <v>4</v>
       </c>
       <c r="H354">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I354">
         <v>5</v>
@@ -18583,19 +18583,19 @@
         <v>454</v>
       </c>
       <c r="E355">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F355">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G355">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H355">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I355">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J355">
         <v>1</v>
@@ -18730,7 +18730,7 @@
         <v>4</v>
       </c>
       <c r="G358">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H358">
         <v>4</v>
@@ -18774,7 +18774,7 @@
         <v>4</v>
       </c>
       <c r="F359">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G359">
         <v>5</v>
@@ -18865,19 +18865,19 @@
         <v>460</v>
       </c>
       <c r="E361">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F361">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G361">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H361">
         <v>5</v>
       </c>
       <c r="I361">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J361">
         <v>2</v>
@@ -18959,19 +18959,19 @@
         <v>462</v>
       </c>
       <c r="E363">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F363">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G363">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H363">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I363">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J363">
         <v>4</v>
@@ -19006,7 +19006,7 @@
         <v>463</v>
       </c>
       <c r="E364">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F364">
         <v>5</v>
@@ -19015,7 +19015,7 @@
         <v>5</v>
       </c>
       <c r="H364">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I364">
         <v>5</v>
@@ -19059,7 +19059,7 @@
         <v>5</v>
       </c>
       <c r="G365">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H365">
         <v>5</v>
@@ -19147,19 +19147,19 @@
         <v>466</v>
       </c>
       <c r="E367">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F367">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G367">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H367">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I367">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J367">
         <v>4</v>
@@ -19194,19 +19194,19 @@
         <v>467</v>
       </c>
       <c r="E368">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F368">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G368">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H368">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I368">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J368">
         <v>1</v>
@@ -19288,19 +19288,19 @@
         <v>469</v>
       </c>
       <c r="E370">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F370">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G370">
         <v>5</v>
       </c>
       <c r="H370">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I370">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J370">
         <v>2</v>
@@ -19382,7 +19382,7 @@
         <v>471</v>
       </c>
       <c r="E372">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F372">
         <v>5</v>
@@ -19391,10 +19391,10 @@
         <v>5</v>
       </c>
       <c r="H372">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I372">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J372">
         <v>3</v>
@@ -19488,7 +19488,7 @@
         <v>5</v>
       </c>
       <c r="I374">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J374">
         <v>3</v>
@@ -19523,7 +19523,7 @@
         <v>474</v>
       </c>
       <c r="E375">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F375">
         <v>5</v>
@@ -19664,19 +19664,19 @@
         <v>477</v>
       </c>
       <c r="E378">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F378">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G378">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H378">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I378">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J378">
         <v>1</v>
@@ -19711,7 +19711,7 @@
         <v>478</v>
       </c>
       <c r="E379">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F379">
         <v>5</v>
@@ -19767,7 +19767,7 @@
         <v>5</v>
       </c>
       <c r="H380">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I380">
         <v>5</v>
@@ -19805,7 +19805,7 @@
         <v>480</v>
       </c>
       <c r="E381">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F381">
         <v>5</v>
@@ -19852,7 +19852,7 @@
         <v>388</v>
       </c>
       <c r="E382">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F382">
         <v>5</v>
@@ -19905,7 +19905,7 @@
         <v>5</v>
       </c>
       <c r="G383">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H383">
         <v>4</v>
@@ -20046,7 +20046,7 @@
         <v>4</v>
       </c>
       <c r="G386">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H386">
         <v>4</v>
@@ -20322,7 +20322,7 @@
         <v>490</v>
       </c>
       <c r="E392">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F392">
         <v>5</v>
@@ -20369,19 +20369,19 @@
         <v>491</v>
       </c>
       <c r="E393">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F393">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G393">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H393">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I393">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J393">
         <v>4</v>
@@ -20560,7 +20560,7 @@
         <v>5</v>
       </c>
       <c r="F397">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G397">
         <v>5</v>
@@ -20604,13 +20604,13 @@
         <v>496</v>
       </c>
       <c r="E398">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F398">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G398">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H398">
         <v>5</v>
@@ -20651,16 +20651,16 @@
         <v>497</v>
       </c>
       <c r="E399">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F399">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G399">
         <v>5</v>
       </c>
       <c r="H399">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I399">
         <v>5</v>
@@ -20792,19 +20792,19 @@
         <v>500</v>
       </c>
       <c r="E402">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F402">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G402">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H402">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I402">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J402">
         <v>3</v>
@@ -20886,19 +20886,19 @@
         <v>502</v>
       </c>
       <c r="E404">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F404">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G404">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H404">
         <v>5</v>
       </c>
       <c r="I404">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J404">
         <v>3</v>
@@ -21268,10 +21268,10 @@
         <v>5</v>
       </c>
       <c r="G412">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H412">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I412">
         <v>5</v>
@@ -21362,7 +21362,7 @@
         <v>4</v>
       </c>
       <c r="G414">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H414">
         <v>3</v>
@@ -21427,10 +21427,10 @@
         <v>4</v>
       </c>
       <c r="M415">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N415">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O415">
         <v>6</v>
@@ -21453,16 +21453,16 @@
         <v>5</v>
       </c>
       <c r="F416">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G416">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H416">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I416">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J416">
         <v>2</v>
@@ -21591,7 +21591,7 @@
         <v>517</v>
       </c>
       <c r="E419">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F419">
         <v>5</v>
@@ -21600,10 +21600,10 @@
         <v>5</v>
       </c>
       <c r="H419">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I419">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J419">
         <v>4</v>
@@ -21653,7 +21653,7 @@
         <v>4</v>
       </c>
       <c r="J420">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K420">
         <v>5</v>

--- a/data/T2_raw.xlsx
+++ b/data/T2_raw.xlsx
@@ -2045,31 +2045,31 @@
         <v>7</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O3">
         <v>6</v>
@@ -2151,19 +2151,19 @@
         <v>5</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O5">
         <v>6</v>
@@ -2198,19 +2198,19 @@
         <v>3</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>6</v>
@@ -2277,34 +2277,34 @@
         <v>110</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8">
         <v>6</v>
@@ -2418,19 +2418,19 @@
         <v>113</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11">
         <v>3</v>
@@ -2515,31 +2515,31 @@
         <v>7</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H13">
         <v>7</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -2559,34 +2559,34 @@
         <v>116</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O14">
         <v>6</v>
@@ -2606,19 +2606,19 @@
         <v>117</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -2841,34 +2841,34 @@
         <v>122</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O20">
         <v>6</v>
@@ -2950,19 +2950,19 @@
         <v>3</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O22">
         <v>6</v>
@@ -3147,7 +3147,7 @@
         <v>1</v>
       </c>
       <c r="M26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N26">
         <v>1</v>
@@ -3185,16 +3185,16 @@
         <v>7</v>
       </c>
       <c r="J27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27">
         <v>1</v>
       </c>
       <c r="L27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N27">
         <v>1</v>
@@ -3217,34 +3217,34 @@
         <v>130</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O28">
         <v>6</v>
@@ -3311,19 +3311,19 @@
         <v>132</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30">
         <v>4</v>
@@ -3452,19 +3452,19 @@
         <v>135</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J33">
         <v>3</v>
@@ -3546,19 +3546,19 @@
         <v>137</v>
       </c>
       <c r="E35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -3593,34 +3593,34 @@
         <v>138</v>
       </c>
       <c r="E36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O36">
         <v>6</v>
@@ -3702,19 +3702,19 @@
         <v>3</v>
       </c>
       <c r="J38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O38">
         <v>6</v>
@@ -3734,19 +3734,19 @@
         <v>141</v>
       </c>
       <c r="E39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I39">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J39">
         <v>2</v>
@@ -3828,19 +3828,19 @@
         <v>143</v>
       </c>
       <c r="E41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J41">
         <v>2</v>
@@ -3969,19 +3969,19 @@
         <v>146</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J44">
         <v>4</v>
@@ -4016,19 +4016,19 @@
         <v>147</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J45">
         <v>4</v>
@@ -4063,34 +4063,34 @@
         <v>148</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46">
         <v>1</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O46">
         <v>6</v>
@@ -4125,19 +4125,19 @@
         <v>5</v>
       </c>
       <c r="J47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M47">
         <v>1</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O47">
         <v>6</v>
@@ -4157,19 +4157,19 @@
         <v>150</v>
       </c>
       <c r="E48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J48">
         <v>3</v>
@@ -4298,34 +4298,34 @@
         <v>153</v>
       </c>
       <c r="E51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G51">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H51">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I51">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O51">
         <v>6</v>
@@ -4345,34 +4345,34 @@
         <v>154</v>
       </c>
       <c r="E52">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F52">
         <v>7</v>
       </c>
       <c r="G52">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I52">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K52">
         <v>1</v>
       </c>
       <c r="L52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O52">
         <v>6</v>
@@ -4407,19 +4407,19 @@
         <v>5</v>
       </c>
       <c r="J53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O53">
         <v>6</v>
@@ -4454,19 +4454,19 @@
         <v>4</v>
       </c>
       <c r="J54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O54">
         <v>6</v>
@@ -4486,19 +4486,19 @@
         <v>157</v>
       </c>
       <c r="E55">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F55">
         <v>7</v>
       </c>
       <c r="G55">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H55">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I55">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -4507,13 +4507,13 @@
         <v>1</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M55">
         <v>1</v>
       </c>
       <c r="N55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O55">
         <v>6</v>
@@ -4536,10 +4536,10 @@
         <v>7</v>
       </c>
       <c r="F56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H56">
         <v>7</v>
@@ -4595,19 +4595,19 @@
         <v>5</v>
       </c>
       <c r="J57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O57">
         <v>6</v>
@@ -4768,34 +4768,34 @@
         <v>163</v>
       </c>
       <c r="E61">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G61">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H61">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I61">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O61">
         <v>6</v>
@@ -4830,19 +4830,19 @@
         <v>5</v>
       </c>
       <c r="J62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O62">
         <v>6</v>
@@ -4909,19 +4909,19 @@
         <v>166</v>
       </c>
       <c r="E64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J64">
         <v>2</v>
@@ -4956,34 +4956,34 @@
         <v>167</v>
       </c>
       <c r="E65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K65">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O65">
         <v>6</v>
@@ -5112,19 +5112,19 @@
         <v>3</v>
       </c>
       <c r="J68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O68">
         <v>6</v>
@@ -5159,19 +5159,19 @@
         <v>6</v>
       </c>
       <c r="J69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O69">
         <v>6</v>
@@ -5206,19 +5206,19 @@
         <v>6</v>
       </c>
       <c r="J70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O70">
         <v>6</v>
@@ -5332,34 +5332,34 @@
         <v>175</v>
       </c>
       <c r="E73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O73">
         <v>6</v>
@@ -5379,34 +5379,34 @@
         <v>176</v>
       </c>
       <c r="E74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O74">
         <v>6</v>
@@ -5426,34 +5426,34 @@
         <v>177</v>
       </c>
       <c r="E75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O75">
         <v>6</v>
@@ -5473,19 +5473,19 @@
         <v>178</v>
       </c>
       <c r="E76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I76">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J76">
         <v>2</v>
@@ -5567,19 +5567,19 @@
         <v>180</v>
       </c>
       <c r="E78">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J78">
         <v>2</v>
@@ -5614,34 +5614,34 @@
         <v>181</v>
       </c>
       <c r="E79">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F79">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G79">
         <v>7</v>
       </c>
       <c r="H79">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I79">
         <v>7</v>
       </c>
       <c r="J79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O79">
         <v>6</v>
@@ -5708,34 +5708,34 @@
         <v>183</v>
       </c>
       <c r="E81">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L81">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N81">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O81">
         <v>6</v>
@@ -5817,19 +5817,19 @@
         <v>3</v>
       </c>
       <c r="J83">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K83">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M83">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N83">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O83">
         <v>6</v>
@@ -6146,19 +6146,19 @@
         <v>3</v>
       </c>
       <c r="J90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L90">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O90">
         <v>6</v>
@@ -6319,34 +6319,34 @@
         <v>196</v>
       </c>
       <c r="E94">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G94">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H94">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K94">
         <v>1</v>
       </c>
       <c r="L94">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M94">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N94">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O94">
         <v>6</v>
@@ -6366,19 +6366,19 @@
         <v>197</v>
       </c>
       <c r="E95">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F95">
         <v>7</v>
       </c>
       <c r="G95">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H95">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I95">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J95">
         <v>2</v>
@@ -6460,19 +6460,19 @@
         <v>199</v>
       </c>
       <c r="E97">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F97">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G97">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I97">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J97">
         <v>2</v>
@@ -6507,19 +6507,19 @@
         <v>200</v>
       </c>
       <c r="E98">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F98">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G98">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H98">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I98">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J98">
         <v>5</v>
@@ -6710,19 +6710,19 @@
         <v>6</v>
       </c>
       <c r="J102">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L102">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O102">
         <v>6</v>
@@ -6745,16 +6745,16 @@
         <v>7</v>
       </c>
       <c r="F103">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G103">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H103">
         <v>7</v>
       </c>
       <c r="I103">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J103">
         <v>2</v>
@@ -6804,19 +6804,19 @@
         <v>6</v>
       </c>
       <c r="J104">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K104">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L104">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M104">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N104">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O104">
         <v>6</v>
@@ -6851,19 +6851,19 @@
         <v>2</v>
       </c>
       <c r="J105">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K105">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L105">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M105">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N105">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O105">
         <v>6</v>
@@ -6977,19 +6977,19 @@
         <v>210</v>
       </c>
       <c r="E108">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F108">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H108">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I108">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J108">
         <v>2</v>
@@ -7024,19 +7024,19 @@
         <v>211</v>
       </c>
       <c r="E109">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H109">
         <v>7</v>
       </c>
       <c r="I109">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J109">
         <v>1</v>
@@ -7212,19 +7212,19 @@
         <v>215</v>
       </c>
       <c r="E113">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F113">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G113">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H113">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I113">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J113">
         <v>3</v>
@@ -7259,19 +7259,19 @@
         <v>216</v>
       </c>
       <c r="E114">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F114">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G114">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J114">
         <v>2</v>
@@ -7509,19 +7509,19 @@
         <v>6</v>
       </c>
       <c r="J119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N119">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O119">
         <v>6</v>
@@ -7556,19 +7556,19 @@
         <v>6</v>
       </c>
       <c r="J120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K120">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M120">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N120">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O120">
         <v>6</v>
@@ -7682,34 +7682,34 @@
         <v>225</v>
       </c>
       <c r="E123">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F123">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G123">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H123">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I123">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J123">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K123">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L123">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M123">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N123">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O123">
         <v>6</v>
@@ -7744,19 +7744,19 @@
         <v>4</v>
       </c>
       <c r="J124">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K124">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L124">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M124">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N124">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O124">
         <v>6</v>
@@ -7776,19 +7776,19 @@
         <v>227</v>
       </c>
       <c r="E125">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F125">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G125">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H125">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I125">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J125">
         <v>1</v>
@@ -7838,19 +7838,19 @@
         <v>4</v>
       </c>
       <c r="J126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K126">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L126">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M126">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O126">
         <v>6</v>
@@ -7917,19 +7917,19 @@
         <v>230</v>
       </c>
       <c r="E128">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F128">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G128">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H128">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I128">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J128">
         <v>3</v>
@@ -7979,19 +7979,19 @@
         <v>7</v>
       </c>
       <c r="J129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K129">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O129">
         <v>6</v>
@@ -8214,19 +8214,19 @@
         <v>5</v>
       </c>
       <c r="J134">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K134">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L134">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N134">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O134">
         <v>6</v>
@@ -8528,34 +8528,34 @@
         <v>243</v>
       </c>
       <c r="E141">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F141">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G141">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H141">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I141">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J141">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K141">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O141">
         <v>6</v>
@@ -8575,19 +8575,19 @@
         <v>244</v>
       </c>
       <c r="E142">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F142">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G142">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H142">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I142">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J142">
         <v>3</v>
@@ -8684,19 +8684,19 @@
         <v>6</v>
       </c>
       <c r="J144">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L144">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N144">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O144">
         <v>6</v>
@@ -8716,19 +8716,19 @@
         <v>247</v>
       </c>
       <c r="E145">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F145">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G145">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H145">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I145">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J145">
         <v>5</v>
@@ -8810,34 +8810,34 @@
         <v>249</v>
       </c>
       <c r="E147">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F147">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G147">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H147">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I147">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J147">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K147">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L147">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M147">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N147">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O147">
         <v>6</v>
@@ -8857,19 +8857,19 @@
         <v>250</v>
       </c>
       <c r="E148">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F148">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G148">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H148">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I148">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J148">
         <v>4</v>
@@ -8998,19 +8998,19 @@
         <v>253</v>
       </c>
       <c r="E151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F151">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G151">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H151">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I151">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J151">
         <v>4</v>
@@ -9045,19 +9045,19 @@
         <v>254</v>
       </c>
       <c r="E152">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F152">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G152">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H152">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I152">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J152">
         <v>2</v>
@@ -9092,19 +9092,19 @@
         <v>255</v>
       </c>
       <c r="E153">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F153">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G153">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H153">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I153">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J153">
         <v>3</v>
@@ -9139,34 +9139,34 @@
         <v>256</v>
       </c>
       <c r="E154">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F154">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G154">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H154">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I154">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J154">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K154">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L154">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M154">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N154">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O154">
         <v>6</v>
@@ -9186,19 +9186,19 @@
         <v>257</v>
       </c>
       <c r="E155">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F155">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G155">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H155">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I155">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J155">
         <v>4</v>
@@ -9233,19 +9233,19 @@
         <v>258</v>
       </c>
       <c r="E156">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F156">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G156">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H156">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I156">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J156">
         <v>1</v>
@@ -9280,19 +9280,19 @@
         <v>259</v>
       </c>
       <c r="E157">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F157">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G157">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H157">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I157">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J157">
         <v>2</v>
@@ -9327,19 +9327,19 @@
         <v>260</v>
       </c>
       <c r="E158">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F158">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G158">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H158">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I158">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J158">
         <v>2</v>
@@ -9483,19 +9483,19 @@
         <v>4</v>
       </c>
       <c r="J161">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K161">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L161">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M161">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N161">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O161">
         <v>6</v>
@@ -9515,19 +9515,19 @@
         <v>264</v>
       </c>
       <c r="E162">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F162">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G162">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H162">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I162">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J162">
         <v>1</v>
@@ -9609,34 +9609,34 @@
         <v>266</v>
       </c>
       <c r="E164">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F164">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G164">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H164">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I164">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J164">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K164">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L164">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M164">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N164">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O164">
         <v>6</v>
@@ -9703,19 +9703,19 @@
         <v>268</v>
       </c>
       <c r="E166">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F166">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G166">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H166">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I166">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J166">
         <v>1</v>
@@ -9844,34 +9844,34 @@
         <v>271</v>
       </c>
       <c r="E169">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F169">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G169">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H169">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I169">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J169">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K169">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L169">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M169">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N169">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O169">
         <v>6</v>
@@ -9906,19 +9906,19 @@
         <v>5</v>
       </c>
       <c r="J170">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K170">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L170">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M170">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N170">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O170">
         <v>6</v>
@@ -9985,19 +9985,19 @@
         <v>274</v>
       </c>
       <c r="E172">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F172">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G172">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H172">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I172">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J172">
         <v>2</v>
@@ -10032,34 +10032,34 @@
         <v>275</v>
       </c>
       <c r="E173">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F173">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G173">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H173">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I173">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J173">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K173">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L173">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M173">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N173">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O173">
         <v>6</v>
@@ -10079,34 +10079,34 @@
         <v>276</v>
       </c>
       <c r="E174">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F174">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G174">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H174">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I174">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J174">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K174">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L174">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M174">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N174">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O174">
         <v>6</v>
@@ -10126,34 +10126,34 @@
         <v>277</v>
       </c>
       <c r="E175">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I175">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L175">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N175">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O175">
         <v>6</v>
@@ -10267,34 +10267,34 @@
         <v>280</v>
       </c>
       <c r="E178">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F178">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G178">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H178">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I178">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J178">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K178">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L178">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M178">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N178">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O178">
         <v>6</v>
@@ -10314,34 +10314,34 @@
         <v>281</v>
       </c>
       <c r="E179">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F179">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G179">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H179">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I179">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J179">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K179">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L179">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M179">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N179">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O179">
         <v>6</v>
@@ -10549,34 +10549,34 @@
         <v>286</v>
       </c>
       <c r="E184">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F184">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G184">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H184">
         <v>7</v>
       </c>
       <c r="I184">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K184">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L184">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M184">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N184">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O184">
         <v>6</v>
@@ -10611,19 +10611,19 @@
         <v>6</v>
       </c>
       <c r="J185">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O185">
         <v>6</v>
@@ -10643,19 +10643,19 @@
         <v>288</v>
       </c>
       <c r="E186">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F186">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G186">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H186">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I186">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J186">
         <v>6</v>
@@ -10831,19 +10831,19 @@
         <v>292</v>
       </c>
       <c r="E190">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F190">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G190">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H190">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I190">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J190">
         <v>2</v>
@@ -10987,19 +10987,19 @@
         <v>6</v>
       </c>
       <c r="J193">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K193">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M193">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O193">
         <v>6</v>
@@ -11034,19 +11034,19 @@
         <v>4</v>
       </c>
       <c r="J194">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K194">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L194">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M194">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N194">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O194">
         <v>6</v>
@@ -11222,19 +11222,19 @@
         <v>5</v>
       </c>
       <c r="J198">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K198">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L198">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M198">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N198">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O198">
         <v>6</v>
@@ -11348,19 +11348,19 @@
         <v>303</v>
       </c>
       <c r="E201">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F201">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G201">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H201">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I201">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J201">
         <v>4</v>
@@ -11442,22 +11442,22 @@
         <v>305</v>
       </c>
       <c r="E203">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F203">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G203">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H203">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I203">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J203">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K203">
         <v>1</v>
@@ -11466,10 +11466,10 @@
         <v>1</v>
       </c>
       <c r="M203">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N203">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O203">
         <v>6</v>
@@ -11536,19 +11536,19 @@
         <v>307</v>
       </c>
       <c r="E205">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F205">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G205">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H205">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I205">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J205">
         <v>3</v>
@@ -11583,34 +11583,34 @@
         <v>308</v>
       </c>
       <c r="E206">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F206">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G206">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H206">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I206">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J206">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K206">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L206">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M206">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N206">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O206">
         <v>6</v>
@@ -11645,19 +11645,19 @@
         <v>3</v>
       </c>
       <c r="J207">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K207">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L207">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M207">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N207">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O207">
         <v>6</v>
@@ -11833,19 +11833,19 @@
         <v>5</v>
       </c>
       <c r="J211">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K211">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L211">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M211">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N211">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O211">
         <v>6</v>
@@ -11880,19 +11880,19 @@
         <v>2</v>
       </c>
       <c r="J212">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K212">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L212">
         <v>7</v>
       </c>
       <c r="M212">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N212">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O212">
         <v>6</v>
@@ -11912,34 +11912,34 @@
         <v>315</v>
       </c>
       <c r="E213">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F213">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G213">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H213">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I213">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J213">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K213">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L213">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M213">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N213">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O213">
         <v>6</v>
@@ -11959,19 +11959,19 @@
         <v>316</v>
       </c>
       <c r="E214">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F214">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G214">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H214">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I214">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J214">
         <v>3</v>
@@ -12006,19 +12006,19 @@
         <v>317</v>
       </c>
       <c r="E215">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F215">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G215">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H215">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I215">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J215">
         <v>5</v>
@@ -12068,19 +12068,19 @@
         <v>6</v>
       </c>
       <c r="J216">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K216">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L216">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M216">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N216">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O216">
         <v>6</v>
@@ -12100,19 +12100,19 @@
         <v>319</v>
       </c>
       <c r="E217">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F217">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G217">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H217">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I217">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J217">
         <v>2</v>
@@ -12162,19 +12162,19 @@
         <v>3</v>
       </c>
       <c r="J218">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K218">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L218">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M218">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N218">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O218">
         <v>6</v>
@@ -12209,19 +12209,19 @@
         <v>5</v>
       </c>
       <c r="J219">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K219">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L219">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M219">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N219">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O219">
         <v>6</v>
@@ -12288,19 +12288,19 @@
         <v>323</v>
       </c>
       <c r="E221">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F221">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G221">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H221">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I221">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J221">
         <v>6</v>
@@ -12350,19 +12350,19 @@
         <v>4</v>
       </c>
       <c r="J222">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K222">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L222">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M222">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N222">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O222">
         <v>6</v>
@@ -12397,19 +12397,19 @@
         <v>3</v>
       </c>
       <c r="J223">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K223">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L223">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M223">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N223">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O223">
         <v>6</v>
@@ -12444,19 +12444,19 @@
         <v>5</v>
       </c>
       <c r="J224">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K224">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L224">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M224">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N224">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O224">
         <v>6</v>
@@ -12476,19 +12476,19 @@
         <v>327</v>
       </c>
       <c r="E225">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F225">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G225">
         <v>7</v>
       </c>
       <c r="H225">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I225">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J225">
         <v>1</v>
@@ -12523,34 +12523,34 @@
         <v>328</v>
       </c>
       <c r="E226">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F226">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G226">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H226">
         <v>7</v>
       </c>
       <c r="I226">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J226">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K226">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L226">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M226">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N226">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O226">
         <v>6</v>
@@ -12585,19 +12585,19 @@
         <v>5</v>
       </c>
       <c r="J227">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K227">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L227">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M227">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N227">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O227">
         <v>6</v>
@@ -12682,16 +12682,16 @@
         <v>1</v>
       </c>
       <c r="K229">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N229">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O229">
         <v>6</v>
@@ -12870,16 +12870,16 @@
         <v>1</v>
       </c>
       <c r="K233">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N233">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O233">
         <v>6</v>
@@ -12899,34 +12899,34 @@
         <v>335</v>
       </c>
       <c r="E234">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F234">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G234">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H234">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I234">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J234">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K234">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L234">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M234">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N234">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O234">
         <v>6</v>
@@ -12961,19 +12961,19 @@
         <v>5</v>
       </c>
       <c r="J235">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K235">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L235">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M235">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N235">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O235">
         <v>6</v>
@@ -12993,19 +12993,19 @@
         <v>337</v>
       </c>
       <c r="E236">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F236">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G236">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H236">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I236">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J236">
         <v>1</v>
@@ -13087,19 +13087,19 @@
         <v>339</v>
       </c>
       <c r="E238">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F238">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G238">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H238">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I238">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J238">
         <v>3</v>
@@ -13149,19 +13149,19 @@
         <v>6</v>
       </c>
       <c r="J239">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K239">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L239">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M239">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N239">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O239">
         <v>6</v>
@@ -13369,34 +13369,34 @@
         <v>345</v>
       </c>
       <c r="E244">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F244">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G244">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H244">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I244">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J244">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K244">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L244">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M244">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N244">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O244">
         <v>6</v>
@@ -13431,19 +13431,19 @@
         <v>3</v>
       </c>
       <c r="J245">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K245">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L245">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M245">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N245">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O245">
         <v>6</v>
@@ -13463,34 +13463,34 @@
         <v>347</v>
       </c>
       <c r="E246">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F246">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G246">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H246">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I246">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J246">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K246">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L246">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M246">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N246">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O246">
         <v>6</v>
@@ -13557,19 +13557,19 @@
         <v>349</v>
       </c>
       <c r="E248">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F248">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G248">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H248">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I248">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J248">
         <v>2</v>
@@ -13666,19 +13666,19 @@
         <v>6</v>
       </c>
       <c r="J250">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K250">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L250">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M250">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N250">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O250">
         <v>6</v>
@@ -13745,19 +13745,19 @@
         <v>353</v>
       </c>
       <c r="E252">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F252">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G252">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H252">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I252">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J252">
         <v>5</v>
@@ -13854,19 +13854,19 @@
         <v>4</v>
       </c>
       <c r="J254">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K254">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L254">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M254">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N254">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O254">
         <v>6</v>
@@ -13886,19 +13886,19 @@
         <v>356</v>
       </c>
       <c r="E255">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F255">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G255">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H255">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I255">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J255">
         <v>2</v>
@@ -13995,19 +13995,19 @@
         <v>5</v>
       </c>
       <c r="J257">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K257">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L257">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M257">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N257">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O257">
         <v>6</v>
@@ -14230,19 +14230,19 @@
         <v>5</v>
       </c>
       <c r="J262">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K262">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L262">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M262">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N262">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O262">
         <v>6</v>
@@ -14262,31 +14262,31 @@
         <v>364</v>
       </c>
       <c r="E263">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F263">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G263">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H263">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I263">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J263">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K263">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L263">
         <v>1</v>
       </c>
       <c r="M263">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N263">
         <v>1</v>
@@ -14356,19 +14356,19 @@
         <v>366</v>
       </c>
       <c r="E265">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F265">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G265">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H265">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I265">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J265">
         <v>2</v>
@@ -14497,34 +14497,34 @@
         <v>369</v>
       </c>
       <c r="E268">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F268">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G268">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H268">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I268">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J268">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K268">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L268">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M268">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N268">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O268">
         <v>6</v>
@@ -14544,34 +14544,34 @@
         <v>370</v>
       </c>
       <c r="E269">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F269">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G269">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H269">
         <v>1</v>
       </c>
       <c r="I269">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J269">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K269">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L269">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M269">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N269">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O269">
         <v>6</v>
@@ -14591,34 +14591,34 @@
         <v>371</v>
       </c>
       <c r="E270">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F270">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G270">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H270">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I270">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J270">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K270">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L270">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M270">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N270">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O270">
         <v>6</v>
@@ -14653,19 +14653,19 @@
         <v>3</v>
       </c>
       <c r="J271">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K271">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L271">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M271">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N271">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O271">
         <v>6</v>
@@ -14685,34 +14685,34 @@
         <v>373</v>
       </c>
       <c r="E272">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F272">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G272">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H272">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I272">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J272">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K272">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L272">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M272">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N272">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O272">
         <v>6</v>
@@ -14747,19 +14747,19 @@
         <v>2</v>
       </c>
       <c r="J273">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K273">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L273">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M273">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N273">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O273">
         <v>6</v>
@@ -14794,19 +14794,19 @@
         <v>4</v>
       </c>
       <c r="J274">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K274">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L274">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M274">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N274">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O274">
         <v>6</v>
@@ -14873,19 +14873,19 @@
         <v>377</v>
       </c>
       <c r="E276">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F276">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G276">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H276">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I276">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J276">
         <v>7</v>
@@ -14935,19 +14935,19 @@
         <v>4</v>
       </c>
       <c r="J277">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K277">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L277">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M277">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N277">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O277">
         <v>6</v>
@@ -14967,34 +14967,34 @@
         <v>379</v>
       </c>
       <c r="E278">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F278">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G278">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H278">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I278">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J278">
         <v>1</v>
       </c>
       <c r="K278">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L278">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M278">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N278">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O278">
         <v>6</v>
@@ -15076,19 +15076,19 @@
         <v>4</v>
       </c>
       <c r="J280">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K280">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L280">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M280">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N280">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O280">
         <v>6</v>
@@ -15155,19 +15155,19 @@
         <v>383</v>
       </c>
       <c r="E282">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F282">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G282">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H282">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I282">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J282">
         <v>3</v>
@@ -15249,19 +15249,19 @@
         <v>385</v>
       </c>
       <c r="E284">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F284">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G284">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H284">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I284">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J284">
         <v>1</v>
@@ -15270,10 +15270,10 @@
         <v>1</v>
       </c>
       <c r="L284">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M284">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N284">
         <v>1</v>
@@ -15317,13 +15317,13 @@
         <v>1</v>
       </c>
       <c r="L285">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M285">
         <v>1</v>
       </c>
       <c r="N285">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O285">
         <v>6</v>
@@ -15346,16 +15346,16 @@
         <v>7</v>
       </c>
       <c r="F286">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G286">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H286">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I286">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J286">
         <v>4</v>
@@ -15390,34 +15390,34 @@
         <v>388</v>
       </c>
       <c r="E287">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F287">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G287">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H287">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I287">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J287">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K287">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L287">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M287">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N287">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O287">
         <v>6</v>
@@ -15484,19 +15484,19 @@
         <v>390</v>
       </c>
       <c r="E289">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F289">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G289">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H289">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I289">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J289">
         <v>2</v>
@@ -15546,19 +15546,19 @@
         <v>3</v>
       </c>
       <c r="J290">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K290">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L290">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M290">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N290">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O290">
         <v>6</v>
@@ -15578,19 +15578,19 @@
         <v>392</v>
       </c>
       <c r="E291">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F291">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G291">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H291">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I291">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J291">
         <v>4</v>
@@ -15687,19 +15687,19 @@
         <v>5</v>
       </c>
       <c r="J293">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K293">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L293">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M293">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N293">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O293">
         <v>6</v>
@@ -15719,19 +15719,19 @@
         <v>395</v>
       </c>
       <c r="E294">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F294">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G294">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H294">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I294">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J294">
         <v>4</v>
@@ -15766,19 +15766,19 @@
         <v>396</v>
       </c>
       <c r="E295">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F295">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G295">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H295">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I295">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J295">
         <v>2</v>
@@ -15813,19 +15813,19 @@
         <v>397</v>
       </c>
       <c r="E296">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F296">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G296">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H296">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I296">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J296">
         <v>2</v>
@@ -15875,19 +15875,19 @@
         <v>2</v>
       </c>
       <c r="J297">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K297">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L297">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M297">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N297">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O297">
         <v>6</v>
@@ -15910,16 +15910,16 @@
         <v>7</v>
       </c>
       <c r="F298">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G298">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H298">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I298">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J298">
         <v>3</v>
@@ -15954,19 +15954,19 @@
         <v>400</v>
       </c>
       <c r="E299">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F299">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G299">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H299">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I299">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J299">
         <v>5</v>
@@ -16001,19 +16001,19 @@
         <v>401</v>
       </c>
       <c r="E300">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F300">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G300">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H300">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I300">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J300">
         <v>1</v>
@@ -16048,19 +16048,19 @@
         <v>402</v>
       </c>
       <c r="E301">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F301">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G301">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H301">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I301">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J301">
         <v>4</v>
@@ -16095,19 +16095,19 @@
         <v>403</v>
       </c>
       <c r="E302">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F302">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G302">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H302">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I302">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J302">
         <v>2</v>
@@ -16189,19 +16189,19 @@
         <v>405</v>
       </c>
       <c r="E304">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F304">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G304">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H304">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I304">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J304">
         <v>4</v>
@@ -16236,34 +16236,34 @@
         <v>406</v>
       </c>
       <c r="E305">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F305">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G305">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H305">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I305">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J305">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K305">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L305">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M305">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N305">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O305">
         <v>6</v>
@@ -16524,7 +16524,7 @@
         <v>7</v>
       </c>
       <c r="G311">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H311">
         <v>7</v>
@@ -16533,16 +16533,16 @@
         <v>7</v>
       </c>
       <c r="J311">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K311">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L311">
         <v>1</v>
       </c>
       <c r="M311">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N311">
         <v>1</v>
@@ -16565,34 +16565,34 @@
         <v>413</v>
       </c>
       <c r="E312">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F312">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G312">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H312">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I312">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J312">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K312">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L312">
         <v>1</v>
       </c>
       <c r="M312">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N312">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O312">
         <v>6</v>
@@ -16612,19 +16612,19 @@
         <v>414</v>
       </c>
       <c r="E313">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F313">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G313">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H313">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I313">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J313">
         <v>4</v>
@@ -16706,19 +16706,19 @@
         <v>416</v>
       </c>
       <c r="E315">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F315">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G315">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H315">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I315">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J315">
         <v>4</v>
@@ -16753,19 +16753,19 @@
         <v>417</v>
       </c>
       <c r="E316">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F316">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G316">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H316">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I316">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J316">
         <v>2</v>
@@ -16800,19 +16800,19 @@
         <v>418</v>
       </c>
       <c r="E317">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F317">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G317">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H317">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I317">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J317">
         <v>1</v>
@@ -17097,19 +17097,19 @@
         <v>5</v>
       </c>
       <c r="J323">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K323">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L323">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M323">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N323">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O323">
         <v>6</v>
@@ -17129,34 +17129,34 @@
         <v>425</v>
       </c>
       <c r="E324">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F324">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G324">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H324">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I324">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J324">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K324">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L324">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M324">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N324">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O324">
         <v>6</v>
@@ -17223,19 +17223,19 @@
         <v>427</v>
       </c>
       <c r="E326">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F326">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G326">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H326">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I326">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J326">
         <v>4</v>
@@ -17317,19 +17317,19 @@
         <v>429</v>
       </c>
       <c r="E328">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F328">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G328">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H328">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I328">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J328">
         <v>3</v>
@@ -17364,19 +17364,19 @@
         <v>430</v>
       </c>
       <c r="E329">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F329">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G329">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H329">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I329">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J329">
         <v>5</v>
@@ -17426,19 +17426,19 @@
         <v>6</v>
       </c>
       <c r="J330">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K330">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L330">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M330">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N330">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O330">
         <v>6</v>
@@ -17567,19 +17567,19 @@
         <v>5</v>
       </c>
       <c r="J333">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K333">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L333">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M333">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N333">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O333">
         <v>6</v>
@@ -17646,19 +17646,19 @@
         <v>436</v>
       </c>
       <c r="E335">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F335">
         <v>7</v>
       </c>
       <c r="G335">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H335">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I335">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J335">
         <v>2</v>
@@ -17714,10 +17714,10 @@
         <v>1</v>
       </c>
       <c r="L336">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M336">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N336">
         <v>1</v>
@@ -17787,19 +17787,19 @@
         <v>439</v>
       </c>
       <c r="E338">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F338">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G338">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H338">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I338">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J338">
         <v>1</v>
@@ -17808,13 +17808,13 @@
         <v>1</v>
       </c>
       <c r="L338">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M338">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N338">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O338">
         <v>6</v>
@@ -17849,19 +17849,19 @@
         <v>3</v>
       </c>
       <c r="J339">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K339">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L339">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M339">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N339">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O339">
         <v>6</v>
@@ -17975,19 +17975,19 @@
         <v>442</v>
       </c>
       <c r="E342">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F342">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G342">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H342">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I342">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J342">
         <v>4</v>
@@ -18116,34 +18116,34 @@
         <v>445</v>
       </c>
       <c r="E345">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F345">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G345">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H345">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I345">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J345">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K345">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L345">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M345">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N345">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O345">
         <v>6</v>
@@ -18163,19 +18163,19 @@
         <v>446</v>
       </c>
       <c r="E346">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F346">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G346">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H346">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I346">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J346">
         <v>4</v>
@@ -18210,19 +18210,19 @@
         <v>447</v>
       </c>
       <c r="E347">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F347">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G347">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H347">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I347">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J347">
         <v>1</v>
@@ -18272,19 +18272,19 @@
         <v>5</v>
       </c>
       <c r="J348">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K348">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L348">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M348">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N348">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O348">
         <v>6</v>
@@ -18413,19 +18413,19 @@
         <v>6</v>
       </c>
       <c r="J351">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K351">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L351">
         <v>1</v>
       </c>
       <c r="M351">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N351">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O351">
         <v>6</v>
@@ -18445,19 +18445,19 @@
         <v>452</v>
       </c>
       <c r="E352">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F352">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G352">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H352">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I352">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J352">
         <v>3</v>
@@ -18492,19 +18492,19 @@
         <v>453</v>
       </c>
       <c r="E353">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F353">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G353">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H353">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I353">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J353">
         <v>3</v>
@@ -18586,19 +18586,19 @@
         <v>455</v>
       </c>
       <c r="E355">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F355">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G355">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H355">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I355">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J355">
         <v>3</v>
@@ -18633,19 +18633,19 @@
         <v>456</v>
       </c>
       <c r="E356">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F356">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G356">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H356">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I356">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J356">
         <v>2</v>
@@ -18695,19 +18695,19 @@
         <v>3</v>
       </c>
       <c r="J357">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K357">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L357">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M357">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N357">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O357">
         <v>6</v>
@@ -18774,19 +18774,19 @@
         <v>459</v>
       </c>
       <c r="E359">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F359">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G359">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H359">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I359">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J359">
         <v>4</v>
@@ -18821,34 +18821,34 @@
         <v>370</v>
       </c>
       <c r="E360">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F360">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G360">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H360">
         <v>1</v>
       </c>
       <c r="I360">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J360">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K360">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L360">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M360">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N360">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O360">
         <v>6</v>
@@ -18871,19 +18871,19 @@
         <v>7</v>
       </c>
       <c r="F361">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G361">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H361">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I361">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J361">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K361">
         <v>1</v>
@@ -18895,7 +18895,7 @@
         <v>1</v>
       </c>
       <c r="N361">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O361">
         <v>6</v>
@@ -18977,19 +18977,19 @@
         <v>4</v>
       </c>
       <c r="J363">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K363">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L363">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M363">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N363">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O363">
         <v>6</v>
@@ -19024,19 +19024,19 @@
         <v>3</v>
       </c>
       <c r="J364">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K364">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L364">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M364">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N364">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O364">
         <v>6</v>
@@ -19118,19 +19118,19 @@
         <v>4</v>
       </c>
       <c r="J366">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K366">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L366">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M366">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N366">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O366">
         <v>6</v>
@@ -19197,19 +19197,19 @@
         <v>467</v>
       </c>
       <c r="E368">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F368">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G368">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H368">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I368">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J368">
         <v>2</v>
@@ -19259,19 +19259,19 @@
         <v>4</v>
       </c>
       <c r="J369">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K369">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L369">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M369">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N369">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O369">
         <v>6</v>
@@ -19291,19 +19291,19 @@
         <v>469</v>
       </c>
       <c r="E370">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F370">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G370">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H370">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I370">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J370">
         <v>2</v>
@@ -19432,19 +19432,19 @@
         <v>472</v>
       </c>
       <c r="E373">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F373">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G373">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H373">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I373">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J373">
         <v>1</v>
@@ -19494,19 +19494,19 @@
         <v>5</v>
       </c>
       <c r="J374">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K374">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L374">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M374">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N374">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O374">
         <v>6</v>
@@ -19526,34 +19526,34 @@
         <v>474</v>
       </c>
       <c r="E375">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F375">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G375">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H375">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I375">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J375">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K375">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L375">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M375">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N375">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O375">
         <v>6</v>
@@ -19573,19 +19573,19 @@
         <v>475</v>
       </c>
       <c r="E376">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F376">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G376">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H376">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I376">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J376">
         <v>4</v>
@@ -19667,19 +19667,19 @@
         <v>477</v>
       </c>
       <c r="E378">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F378">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G378">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H378">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I378">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J378">
         <v>4</v>
@@ -19717,16 +19717,16 @@
         <v>7</v>
       </c>
       <c r="F379">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G379">
         <v>7</v>
       </c>
       <c r="H379">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I379">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J379">
         <v>1</v>
@@ -19808,19 +19808,19 @@
         <v>480</v>
       </c>
       <c r="E381">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F381">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G381">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H381">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I381">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J381">
         <v>4</v>
@@ -19902,19 +19902,19 @@
         <v>482</v>
       </c>
       <c r="E383">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F383">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G383">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H383">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I383">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J383">
         <v>4</v>
@@ -19949,34 +19949,34 @@
         <v>483</v>
       </c>
       <c r="E384">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F384">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G384">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H384">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I384">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J384">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K384">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L384">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M384">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N384">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O384">
         <v>6</v>
@@ -19996,34 +19996,34 @@
         <v>484</v>
       </c>
       <c r="E385">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F385">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G385">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H385">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I385">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J385">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K385">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L385">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M385">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N385">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O385">
         <v>6</v>
@@ -20043,34 +20043,34 @@
         <v>485</v>
       </c>
       <c r="E386">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F386">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G386">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H386">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I386">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J386">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K386">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L386">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M386">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N386">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O386">
         <v>6</v>
@@ -20137,34 +20137,34 @@
         <v>487</v>
       </c>
       <c r="E388">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F388">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G388">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H388">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I388">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J388">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K388">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L388">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M388">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N388">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O388">
         <v>6</v>
@@ -20184,34 +20184,34 @@
         <v>488</v>
       </c>
       <c r="E389">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F389">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G389">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H389">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I389">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J389">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K389">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L389">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M389">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N389">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O389">
         <v>6</v>
@@ -20246,19 +20246,19 @@
         <v>3</v>
       </c>
       <c r="J390">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K390">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L390">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M390">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N390">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O390">
         <v>6</v>
@@ -20387,19 +20387,19 @@
         <v>4</v>
       </c>
       <c r="J393">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K393">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L393">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M393">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N393">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O393">
         <v>6</v>
@@ -20528,19 +20528,19 @@
         <v>4</v>
       </c>
       <c r="J396">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K396">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L396">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M396">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N396">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O396">
         <v>6</v>
@@ -20560,19 +20560,19 @@
         <v>496</v>
       </c>
       <c r="E397">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F397">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G397">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H397">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I397">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J397">
         <v>2</v>
@@ -20748,34 +20748,34 @@
         <v>500</v>
       </c>
       <c r="E401">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F401">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G401">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H401">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I401">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J401">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K401">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L401">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M401">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N401">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O401">
         <v>6</v>
@@ -20795,19 +20795,19 @@
         <v>501</v>
       </c>
       <c r="E402">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F402">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G402">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H402">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I402">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J402">
         <v>6</v>
@@ -20842,19 +20842,19 @@
         <v>502</v>
       </c>
       <c r="E403">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F403">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G403">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H403">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I403">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J403">
         <v>4</v>
@@ -20889,19 +20889,19 @@
         <v>503</v>
       </c>
       <c r="E404">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F404">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G404">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H404">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I404">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J404">
         <v>6</v>
@@ -20951,19 +20951,19 @@
         <v>4</v>
       </c>
       <c r="J405">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K405">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L405">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M405">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N405">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O405">
         <v>6</v>
@@ -20998,19 +20998,19 @@
         <v>3</v>
       </c>
       <c r="J406">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K406">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L406">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M406">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N406">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O406">
         <v>6</v>
@@ -21030,19 +21030,19 @@
         <v>506</v>
       </c>
       <c r="E407">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F407">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G407">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H407">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I407">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J407">
         <v>2</v>
@@ -21095,16 +21095,16 @@
         <v>1</v>
       </c>
       <c r="K408">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L408">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M408">
         <v>1</v>
       </c>
       <c r="N408">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O408">
         <v>6</v>
@@ -21186,19 +21186,19 @@
         <v>3</v>
       </c>
       <c r="J410">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K410">
         <v>1</v>
       </c>
       <c r="L410">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M410">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N410">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O410">
         <v>6</v>
@@ -21221,16 +21221,16 @@
         <v>7</v>
       </c>
       <c r="F411">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G411">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H411">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I411">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J411">
         <v>4</v>
@@ -21424,13 +21424,13 @@
         <v>1</v>
       </c>
       <c r="K415">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L415">
         <v>1</v>
       </c>
       <c r="M415">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N415">
         <v>1</v>
@@ -21453,19 +21453,19 @@
         <v>514</v>
       </c>
       <c r="E416">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F416">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G416">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H416">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I416">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J416">
         <v>1</v>
@@ -21474,13 +21474,13 @@
         <v>1</v>
       </c>
       <c r="L416">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M416">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N416">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O416">
         <v>6</v>
@@ -21547,19 +21547,19 @@
         <v>516</v>
       </c>
       <c r="E418">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F418">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G418">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H418">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I418">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J418">
         <v>1</v>
@@ -21594,19 +21594,19 @@
         <v>517</v>
       </c>
       <c r="E419">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F419">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G419">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H419">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I419">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J419">
         <v>3</v>
@@ -21641,19 +21641,19 @@
         <v>518</v>
       </c>
       <c r="E420">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F420">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G420">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H420">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I420">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J420">
         <v>4</v>
@@ -21703,19 +21703,19 @@
         <v>3</v>
       </c>
       <c r="J421">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K421">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L421">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M421">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N421">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O421">
         <v>6</v>

--- a/data/T2_raw.xlsx
+++ b/data/T2_raw.xlsx
@@ -2010,19 +2010,19 @@
         <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O2">
         <v>6</v>
@@ -2110,7 +2110,7 @@
         <v>3</v>
       </c>
       <c r="L4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M4">
         <v>2</v>
@@ -2157,7 +2157,7 @@
         <v>2</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -2248,13 +2248,13 @@
         <v>2</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N7">
         <v>1</v>
@@ -2298,10 +2298,10 @@
         <v>3</v>
       </c>
       <c r="L8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N8">
         <v>3</v>
@@ -2489,10 +2489,10 @@
         <v>4</v>
       </c>
       <c r="M12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O12">
         <v>6</v>
@@ -2668,16 +2668,16 @@
         <v>6</v>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16">
         <v>3</v>
       </c>
       <c r="L16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N16">
         <v>3</v>
@@ -2715,19 +2715,19 @@
         <v>5</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O17">
         <v>6</v>
@@ -2762,19 +2762,19 @@
         <v>5</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18">
         <v>1</v>
       </c>
       <c r="N18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O18">
         <v>6</v>
@@ -2809,19 +2809,19 @@
         <v>5</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19">
         <v>2</v>
       </c>
       <c r="M19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -2903,16 +2903,16 @@
         <v>5</v>
       </c>
       <c r="J21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N21">
         <v>2</v>
@@ -2950,19 +2950,19 @@
         <v>4</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>6</v>
@@ -3000,7 +3000,7 @@
         <v>4</v>
       </c>
       <c r="K23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L23">
         <v>4</v>
@@ -3044,7 +3044,7 @@
         <v>5</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K24">
         <v>4</v>
@@ -3053,7 +3053,7 @@
         <v>5</v>
       </c>
       <c r="M24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>4</v>
@@ -3091,19 +3091,19 @@
         <v>3</v>
       </c>
       <c r="J25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L25">
         <v>4</v>
       </c>
       <c r="M25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -3235,7 +3235,7 @@
         <v>4</v>
       </c>
       <c r="K28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L28">
         <v>3</v>
@@ -3329,13 +3329,13 @@
         <v>3</v>
       </c>
       <c r="K30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L30">
         <v>3</v>
       </c>
       <c r="M30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N30">
         <v>2</v>
@@ -3373,16 +3373,16 @@
         <v>4</v>
       </c>
       <c r="J31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N31">
         <v>5</v>
@@ -3514,16 +3514,16 @@
         <v>3</v>
       </c>
       <c r="J34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L34">
         <v>4</v>
       </c>
       <c r="M34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N34">
         <v>4</v>
@@ -3620,7 +3620,7 @@
         <v>2</v>
       </c>
       <c r="N36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O36">
         <v>6</v>
@@ -3658,10 +3658,10 @@
         <v>4</v>
       </c>
       <c r="K37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M37">
         <v>4</v>
@@ -3702,7 +3702,7 @@
         <v>5</v>
       </c>
       <c r="J38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K38">
         <v>3</v>
@@ -3711,10 +3711,10 @@
         <v>2</v>
       </c>
       <c r="M38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O38">
         <v>6</v>
@@ -3752,16 +3752,16 @@
         <v>4</v>
       </c>
       <c r="K39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O39">
         <v>6</v>
@@ -3796,19 +3796,19 @@
         <v>3</v>
       </c>
       <c r="J40">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N40">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O40">
         <v>6</v>
@@ -3846,7 +3846,7 @@
         <v>2</v>
       </c>
       <c r="K41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L41">
         <v>1</v>
@@ -3890,19 +3890,19 @@
         <v>2</v>
       </c>
       <c r="J42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N42">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -4034,13 +4034,13 @@
         <v>3</v>
       </c>
       <c r="K45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N45">
         <v>2</v>
@@ -4178,7 +4178,7 @@
         <v>5</v>
       </c>
       <c r="L48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M48">
         <v>4</v>
@@ -4219,16 +4219,16 @@
         <v>4</v>
       </c>
       <c r="J49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M49">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N49">
         <v>4</v>
@@ -4266,19 +4266,19 @@
         <v>6</v>
       </c>
       <c r="J50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O50">
         <v>6</v>
@@ -4313,19 +4313,19 @@
         <v>7</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M51">
         <v>3</v>
       </c>
       <c r="N51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O51">
         <v>6</v>
@@ -4363,7 +4363,7 @@
         <v>1</v>
       </c>
       <c r="K52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L52">
         <v>1</v>
@@ -4407,19 +4407,19 @@
         <v>6</v>
       </c>
       <c r="J53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O53">
         <v>6</v>
@@ -4504,13 +4504,13 @@
         <v>1</v>
       </c>
       <c r="K55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N55">
         <v>1</v>
@@ -4548,16 +4548,16 @@
         <v>7</v>
       </c>
       <c r="J56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L56">
         <v>4</v>
       </c>
       <c r="M56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N56">
         <v>2</v>
@@ -4598,16 +4598,16 @@
         <v>2</v>
       </c>
       <c r="K57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O57">
         <v>6</v>
@@ -4695,7 +4695,7 @@
         <v>1</v>
       </c>
       <c r="L59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M59">
         <v>1</v>
@@ -4745,10 +4745,10 @@
         <v>3</v>
       </c>
       <c r="M60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N60">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O60">
         <v>6</v>
@@ -4927,7 +4927,7 @@
         <v>3</v>
       </c>
       <c r="K64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L64">
         <v>3</v>
@@ -5112,7 +5112,7 @@
         <v>3</v>
       </c>
       <c r="J68">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K68">
         <v>5</v>
@@ -5159,19 +5159,19 @@
         <v>3</v>
       </c>
       <c r="J69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O69">
         <v>6</v>
@@ -5206,19 +5206,19 @@
         <v>7</v>
       </c>
       <c r="J70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O70">
         <v>6</v>
@@ -5256,7 +5256,7 @@
         <v>4</v>
       </c>
       <c r="K71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L71">
         <v>3</v>
@@ -5394,19 +5394,19 @@
         <v>2</v>
       </c>
       <c r="J74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O74">
         <v>6</v>
@@ -5441,16 +5441,16 @@
         <v>3</v>
       </c>
       <c r="J75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N75">
         <v>3</v>
@@ -5488,19 +5488,19 @@
         <v>4</v>
       </c>
       <c r="J76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O76">
         <v>6</v>
@@ -5535,19 +5535,19 @@
         <v>7</v>
       </c>
       <c r="J77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N77">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O77">
         <v>6</v>
@@ -5582,19 +5582,19 @@
         <v>7</v>
       </c>
       <c r="J78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O78">
         <v>6</v>
@@ -5632,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="K79">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L79">
         <v>4</v>
@@ -5679,10 +5679,10 @@
         <v>2</v>
       </c>
       <c r="K80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M80">
         <v>1</v>
@@ -5723,19 +5723,19 @@
         <v>3</v>
       </c>
       <c r="J81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K81">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L81">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O81">
         <v>6</v>
@@ -5782,7 +5782,7 @@
         <v>1</v>
       </c>
       <c r="N82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O82">
         <v>6</v>
@@ -5817,7 +5817,7 @@
         <v>5</v>
       </c>
       <c r="J83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K83">
         <v>4</v>
@@ -5829,7 +5829,7 @@
         <v>4</v>
       </c>
       <c r="N83">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O83">
         <v>6</v>
@@ -5864,19 +5864,19 @@
         <v>7</v>
       </c>
       <c r="J84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O84">
         <v>6</v>
@@ -6008,7 +6008,7 @@
         <v>3</v>
       </c>
       <c r="K87">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L87">
         <v>3</v>
@@ -6099,19 +6099,19 @@
         <v>4</v>
       </c>
       <c r="J89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K89">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O89">
         <v>6</v>
@@ -6146,19 +6146,19 @@
         <v>2</v>
       </c>
       <c r="J90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K90">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O90">
         <v>6</v>
@@ -6193,19 +6193,19 @@
         <v>7</v>
       </c>
       <c r="J91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M91">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N91">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O91">
         <v>6</v>
@@ -6290,13 +6290,13 @@
         <v>2</v>
       </c>
       <c r="K93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L93">
         <v>3</v>
       </c>
       <c r="M93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N93">
         <v>2</v>
@@ -6334,19 +6334,19 @@
         <v>4</v>
       </c>
       <c r="J94">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M94">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O94">
         <v>6</v>
@@ -6381,19 +6381,19 @@
         <v>7</v>
       </c>
       <c r="J95">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K95">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L95">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M95">
         <v>3</v>
       </c>
       <c r="N95">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O95">
         <v>6</v>
@@ -6428,19 +6428,19 @@
         <v>7</v>
       </c>
       <c r="J96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K96">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M96">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O96">
         <v>6</v>
@@ -6522,19 +6522,19 @@
         <v>4</v>
       </c>
       <c r="J98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L98">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M98">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O98">
         <v>6</v>
@@ -6569,19 +6569,19 @@
         <v>5</v>
       </c>
       <c r="J99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L99">
         <v>2</v>
       </c>
       <c r="M99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O99">
         <v>6</v>
@@ -6666,16 +6666,16 @@
         <v>1</v>
       </c>
       <c r="K101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M101">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O101">
         <v>6</v>
@@ -6804,16 +6804,16 @@
         <v>3</v>
       </c>
       <c r="J104">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L104">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N104">
         <v>3</v>
@@ -6857,7 +6857,7 @@
         <v>3</v>
       </c>
       <c r="L105">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M105">
         <v>6</v>
@@ -6898,19 +6898,19 @@
         <v>6</v>
       </c>
       <c r="J106">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K106">
         <v>3</v>
       </c>
       <c r="L106">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M106">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N106">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O106">
         <v>6</v>
@@ -6995,16 +6995,16 @@
         <v>4</v>
       </c>
       <c r="K108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M108">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N108">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O108">
         <v>6</v>
@@ -7039,19 +7039,19 @@
         <v>6</v>
       </c>
       <c r="J109">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K109">
         <v>1</v>
       </c>
       <c r="L109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M109">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N109">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O109">
         <v>6</v>
@@ -7086,16 +7086,16 @@
         <v>7</v>
       </c>
       <c r="J110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K110">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M110">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N110">
         <v>1</v>
@@ -7227,7 +7227,7 @@
         <v>5</v>
       </c>
       <c r="J113">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K113">
         <v>3</v>
@@ -7330,7 +7330,7 @@
         <v>1</v>
       </c>
       <c r="M115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N115">
         <v>2</v>
@@ -7368,19 +7368,19 @@
         <v>1</v>
       </c>
       <c r="J116">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K116">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L116">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M116">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N116">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O116">
         <v>6</v>
@@ -7509,19 +7509,19 @@
         <v>4</v>
       </c>
       <c r="J119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N119">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O119">
         <v>6</v>
@@ -7556,13 +7556,13 @@
         <v>4</v>
       </c>
       <c r="J120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K120">
         <v>1</v>
       </c>
       <c r="L120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M120">
         <v>1</v>
@@ -7650,19 +7650,19 @@
         <v>3</v>
       </c>
       <c r="J122">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K122">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L122">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M122">
         <v>4</v>
       </c>
       <c r="N122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O122">
         <v>6</v>
@@ -7697,19 +7697,19 @@
         <v>3</v>
       </c>
       <c r="J123">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K123">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L123">
         <v>3</v>
       </c>
       <c r="M123">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N123">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O123">
         <v>6</v>
@@ -7744,7 +7744,7 @@
         <v>4</v>
       </c>
       <c r="J124">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K124">
         <v>3</v>
@@ -7756,7 +7756,7 @@
         <v>4</v>
       </c>
       <c r="N124">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O124">
         <v>6</v>
@@ -7935,13 +7935,13 @@
         <v>3</v>
       </c>
       <c r="K128">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L128">
         <v>3</v>
       </c>
       <c r="M128">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N128">
         <v>4</v>
@@ -7979,13 +7979,13 @@
         <v>6</v>
       </c>
       <c r="J129">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K129">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L129">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M129">
         <v>5</v>
@@ -8226,7 +8226,7 @@
         <v>2</v>
       </c>
       <c r="N134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O134">
         <v>6</v>
@@ -8273,7 +8273,7 @@
         <v>5</v>
       </c>
       <c r="N135">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O135">
         <v>6</v>
@@ -8355,13 +8355,13 @@
         <v>4</v>
       </c>
       <c r="J137">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K137">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L137">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M137">
         <v>7</v>
@@ -8402,19 +8402,19 @@
         <v>7</v>
       </c>
       <c r="J138">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K138">
         <v>3</v>
       </c>
       <c r="L138">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N138">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O138">
         <v>6</v>
@@ -8496,19 +8496,19 @@
         <v>5</v>
       </c>
       <c r="J140">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K140">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L140">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M140">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N140">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O140">
         <v>6</v>
@@ -8543,19 +8543,19 @@
         <v>3</v>
       </c>
       <c r="J141">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K141">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L141">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M141">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N141">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O141">
         <v>6</v>
@@ -8590,19 +8590,19 @@
         <v>2</v>
       </c>
       <c r="J142">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K142">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L142">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M142">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N142">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O142">
         <v>6</v>
@@ -8684,19 +8684,19 @@
         <v>6</v>
       </c>
       <c r="J144">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K144">
         <v>3</v>
       </c>
       <c r="L144">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M144">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N144">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O144">
         <v>6</v>
@@ -8731,19 +8731,19 @@
         <v>3</v>
       </c>
       <c r="J145">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K145">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M145">
         <v>2</v>
       </c>
       <c r="N145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O145">
         <v>6</v>
@@ -8778,19 +8778,19 @@
         <v>4</v>
       </c>
       <c r="J146">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K146">
         <v>3</v>
       </c>
       <c r="L146">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N146">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O146">
         <v>6</v>
@@ -8828,7 +8828,7 @@
         <v>4</v>
       </c>
       <c r="K147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L147">
         <v>3</v>
@@ -8872,19 +8872,19 @@
         <v>5</v>
       </c>
       <c r="J148">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L148">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M148">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N148">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O148">
         <v>6</v>
@@ -9016,7 +9016,7 @@
         <v>4</v>
       </c>
       <c r="K151">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L151">
         <v>3</v>
@@ -9060,7 +9060,7 @@
         <v>5</v>
       </c>
       <c r="J152">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K152">
         <v>5</v>
@@ -9163,7 +9163,7 @@
         <v>3</v>
       </c>
       <c r="M154">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N154">
         <v>4</v>
@@ -9201,19 +9201,19 @@
         <v>6</v>
       </c>
       <c r="J155">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K155">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L155">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M155">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N155">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O155">
         <v>6</v>
@@ -9254,7 +9254,7 @@
         <v>3</v>
       </c>
       <c r="L156">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M156">
         <v>4</v>
@@ -9307,7 +9307,7 @@
         <v>4</v>
       </c>
       <c r="N157">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O157">
         <v>6</v>
@@ -9345,16 +9345,16 @@
         <v>6</v>
       </c>
       <c r="K158">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L158">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M158">
         <v>4</v>
       </c>
       <c r="N158">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O158">
         <v>6</v>
@@ -9392,16 +9392,16 @@
         <v>1</v>
       </c>
       <c r="K159">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L159">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M159">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N159">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O159">
         <v>6</v>
@@ -9533,10 +9533,10 @@
         <v>1</v>
       </c>
       <c r="K162">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L162">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M162">
         <v>1</v>
@@ -9586,7 +9586,7 @@
         <v>4</v>
       </c>
       <c r="M163">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N163">
         <v>2</v>
@@ -9624,7 +9624,7 @@
         <v>6</v>
       </c>
       <c r="J164">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K164">
         <v>3</v>
@@ -9633,7 +9633,7 @@
         <v>3</v>
       </c>
       <c r="M164">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N164">
         <v>4</v>
@@ -9671,19 +9671,19 @@
         <v>7</v>
       </c>
       <c r="J165">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K165">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L165">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M165">
         <v>3</v>
       </c>
       <c r="N165">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O165">
         <v>6</v>
@@ -9721,16 +9721,16 @@
         <v>4</v>
       </c>
       <c r="K166">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L166">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M166">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N166">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O166">
         <v>6</v>
@@ -9824,7 +9824,7 @@
         <v>3</v>
       </c>
       <c r="N168">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O168">
         <v>6</v>
@@ -9859,19 +9859,19 @@
         <v>3</v>
       </c>
       <c r="J169">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K169">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L169">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M169">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N169">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O169">
         <v>6</v>
@@ -9965,7 +9965,7 @@
         <v>1</v>
       </c>
       <c r="N171">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O171">
         <v>6</v>
@@ -10003,7 +10003,7 @@
         <v>3</v>
       </c>
       <c r="K172">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L172">
         <v>3</v>
@@ -10097,13 +10097,13 @@
         <v>3</v>
       </c>
       <c r="K174">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L174">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M174">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N174">
         <v>3</v>
@@ -10188,10 +10188,10 @@
         <v>5</v>
       </c>
       <c r="J176">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K176">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L176">
         <v>3</v>
@@ -10282,19 +10282,19 @@
         <v>4</v>
       </c>
       <c r="J178">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K178">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L178">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M178">
         <v>4</v>
       </c>
       <c r="N178">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O178">
         <v>6</v>
@@ -10329,19 +10329,19 @@
         <v>5</v>
       </c>
       <c r="J179">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K179">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L179">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M179">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N179">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O179">
         <v>6</v>
@@ -10376,19 +10376,19 @@
         <v>6</v>
       </c>
       <c r="J180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K180">
         <v>3</v>
       </c>
       <c r="L180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M180">
         <v>4</v>
       </c>
       <c r="N180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O180">
         <v>6</v>
@@ -10423,19 +10423,19 @@
         <v>5</v>
       </c>
       <c r="J181">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K181">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L181">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N181">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O181">
         <v>6</v>
@@ -10479,7 +10479,7 @@
         <v>3</v>
       </c>
       <c r="M182">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N182">
         <v>2</v>
@@ -10564,7 +10564,7 @@
         <v>6</v>
       </c>
       <c r="J184">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K184">
         <v>1</v>
@@ -10717,7 +10717,7 @@
         <v>3</v>
       </c>
       <c r="N187">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O187">
         <v>6</v>
@@ -10755,7 +10755,7 @@
         <v>3</v>
       </c>
       <c r="K188">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L188">
         <v>4</v>
@@ -10893,10 +10893,10 @@
         <v>5</v>
       </c>
       <c r="J191">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K191">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L191">
         <v>1</v>
@@ -10940,19 +10940,19 @@
         <v>5</v>
       </c>
       <c r="J192">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K192">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L192">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M192">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N192">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O192">
         <v>6</v>
@@ -10993,10 +10993,10 @@
         <v>4</v>
       </c>
       <c r="L193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N193">
         <v>3</v>
@@ -11043,10 +11043,10 @@
         <v>5</v>
       </c>
       <c r="M194">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N194">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O194">
         <v>6</v>
@@ -11081,16 +11081,16 @@
         <v>4</v>
       </c>
       <c r="J195">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K195">
         <v>3</v>
       </c>
       <c r="L195">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M195">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N195">
         <v>4</v>
@@ -11457,19 +11457,19 @@
         <v>7</v>
       </c>
       <c r="J203">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K203">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L203">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M203">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N203">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O203">
         <v>6</v>
@@ -11507,10 +11507,10 @@
         <v>4</v>
       </c>
       <c r="K204">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L204">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M204">
         <v>5</v>
@@ -11551,19 +11551,19 @@
         <v>1</v>
       </c>
       <c r="J205">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K205">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L205">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M205">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N205">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O205">
         <v>6</v>
@@ -11598,10 +11598,10 @@
         <v>4</v>
       </c>
       <c r="J206">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K206">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L206">
         <v>4</v>
@@ -11645,7 +11645,7 @@
         <v>3</v>
       </c>
       <c r="J207">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K207">
         <v>5</v>
@@ -11786,16 +11786,16 @@
         <v>6</v>
       </c>
       <c r="J210">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K210">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L210">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M210">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N210">
         <v>4</v>
@@ -11833,19 +11833,19 @@
         <v>3</v>
       </c>
       <c r="J211">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K211">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L211">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M211">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N211">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O211">
         <v>6</v>
@@ -11880,19 +11880,19 @@
         <v>2</v>
       </c>
       <c r="J212">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K212">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L212">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M212">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N212">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O212">
         <v>6</v>
@@ -11927,7 +11927,7 @@
         <v>2</v>
       </c>
       <c r="J213">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K213">
         <v>2</v>
@@ -11974,19 +11974,19 @@
         <v>4</v>
       </c>
       <c r="J214">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K214">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L214">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M214">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N214">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O214">
         <v>6</v>
@@ -12030,10 +12030,10 @@
         <v>5</v>
       </c>
       <c r="M215">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N215">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O215">
         <v>6</v>
@@ -12068,19 +12068,19 @@
         <v>4</v>
       </c>
       <c r="J216">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K216">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L216">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M216">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N216">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O216">
         <v>6</v>
@@ -12118,7 +12118,7 @@
         <v>4</v>
       </c>
       <c r="K217">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L217">
         <v>4</v>
@@ -12162,10 +12162,10 @@
         <v>4</v>
       </c>
       <c r="J218">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K218">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L218">
         <v>2</v>
@@ -12174,7 +12174,7 @@
         <v>2</v>
       </c>
       <c r="N218">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O218">
         <v>6</v>
@@ -12218,7 +12218,7 @@
         <v>3</v>
       </c>
       <c r="M219">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N219">
         <v>3</v>
@@ -12303,19 +12303,19 @@
         <v>1</v>
       </c>
       <c r="J221">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K221">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L221">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M221">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N221">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O221">
         <v>6</v>
@@ -12353,16 +12353,16 @@
         <v>4</v>
       </c>
       <c r="K222">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L222">
         <v>4</v>
       </c>
       <c r="M222">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N222">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O222">
         <v>6</v>
@@ -12444,7 +12444,7 @@
         <v>5</v>
       </c>
       <c r="J224">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K224">
         <v>2</v>
@@ -12494,7 +12494,7 @@
         <v>2</v>
       </c>
       <c r="K225">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L225">
         <v>1</v>
@@ -12503,7 +12503,7 @@
         <v>4</v>
       </c>
       <c r="N225">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O225">
         <v>6</v>
@@ -12594,10 +12594,10 @@
         <v>3</v>
       </c>
       <c r="M227">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N227">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O227">
         <v>6</v>
@@ -12679,16 +12679,16 @@
         <v>3</v>
       </c>
       <c r="J229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M229">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N229">
         <v>1</v>
@@ -12829,7 +12829,7 @@
         <v>2</v>
       </c>
       <c r="M232">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N232">
         <v>1</v>
@@ -12867,16 +12867,16 @@
         <v>3</v>
       </c>
       <c r="J233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N233">
         <v>1</v>
@@ -12961,19 +12961,19 @@
         <v>4</v>
       </c>
       <c r="J235">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K235">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L235">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M235">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N235">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O235">
         <v>6</v>
@@ -13055,10 +13055,10 @@
         <v>3</v>
       </c>
       <c r="J237">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K237">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L237">
         <v>2</v>
@@ -13067,7 +13067,7 @@
         <v>2</v>
       </c>
       <c r="N237">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O237">
         <v>6</v>
@@ -13114,7 +13114,7 @@
         <v>1</v>
       </c>
       <c r="N238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O238">
         <v>6</v>
@@ -13196,10 +13196,10 @@
         <v>6</v>
       </c>
       <c r="J240">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K240">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L240">
         <v>2</v>
@@ -13208,7 +13208,7 @@
         <v>2</v>
       </c>
       <c r="N240">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O240">
         <v>6</v>
@@ -13249,7 +13249,7 @@
         <v>2</v>
       </c>
       <c r="L241">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M241">
         <v>1</v>
@@ -13343,7 +13343,7 @@
         <v>2</v>
       </c>
       <c r="L243">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M243">
         <v>1</v>
@@ -13478,19 +13478,19 @@
         <v>5</v>
       </c>
       <c r="J246">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K246">
         <v>3</v>
       </c>
       <c r="L246">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M246">
         <v>3</v>
       </c>
       <c r="N246">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O246">
         <v>6</v>
@@ -13525,16 +13525,16 @@
         <v>5</v>
       </c>
       <c r="J247">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K247">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L247">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M247">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N247">
         <v>3</v>
@@ -13572,19 +13572,19 @@
         <v>5</v>
       </c>
       <c r="J248">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K248">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L248">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M248">
         <v>3</v>
       </c>
       <c r="N248">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O248">
         <v>6</v>
@@ -13619,19 +13619,19 @@
         <v>6</v>
       </c>
       <c r="J249">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K249">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L249">
         <v>4</v>
       </c>
       <c r="M249">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N249">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O249">
         <v>6</v>
@@ -13666,10 +13666,10 @@
         <v>6</v>
       </c>
       <c r="J250">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K250">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L250">
         <v>3</v>
@@ -13678,7 +13678,7 @@
         <v>1</v>
       </c>
       <c r="N250">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O250">
         <v>6</v>
@@ -13719,7 +13719,7 @@
         <v>2</v>
       </c>
       <c r="L251">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M251">
         <v>2</v>
@@ -13772,7 +13772,7 @@
         <v>5</v>
       </c>
       <c r="N252">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O252">
         <v>6</v>
@@ -13807,19 +13807,19 @@
         <v>4</v>
       </c>
       <c r="J253">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K253">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L253">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M253">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N253">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O253">
         <v>6</v>
@@ -13854,19 +13854,19 @@
         <v>5</v>
       </c>
       <c r="J254">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K254">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L254">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M254">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N254">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O254">
         <v>6</v>
@@ -13907,7 +13907,7 @@
         <v>3</v>
       </c>
       <c r="L255">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M255">
         <v>2</v>
@@ -14095,7 +14095,7 @@
         <v>1</v>
       </c>
       <c r="L259">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M259">
         <v>1</v>
@@ -14242,7 +14242,7 @@
         <v>1</v>
       </c>
       <c r="N262">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O262">
         <v>6</v>
@@ -14286,7 +14286,7 @@
         <v>1</v>
       </c>
       <c r="M263">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N263">
         <v>2</v>
@@ -14330,10 +14330,10 @@
         <v>5</v>
       </c>
       <c r="L264">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M264">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N264">
         <v>5</v>
@@ -14565,7 +14565,7 @@
         <v>4</v>
       </c>
       <c r="L269">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M269">
         <v>4</v>
@@ -14700,19 +14700,19 @@
         <v>4</v>
       </c>
       <c r="J272">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K272">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L272">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M272">
         <v>2</v>
       </c>
       <c r="N272">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O272">
         <v>6</v>
@@ -14794,19 +14794,19 @@
         <v>4</v>
       </c>
       <c r="J274">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K274">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L274">
         <v>5</v>
       </c>
       <c r="M274">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N274">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O274">
         <v>6</v>
@@ -14888,13 +14888,13 @@
         <v>1</v>
       </c>
       <c r="J276">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K276">
         <v>3</v>
       </c>
       <c r="L276">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M276">
         <v>4</v>
@@ -14938,16 +14938,16 @@
         <v>4</v>
       </c>
       <c r="K277">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L277">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M277">
         <v>4</v>
       </c>
       <c r="N277">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O277">
         <v>6</v>
@@ -15082,10 +15082,10 @@
         <v>1</v>
       </c>
       <c r="L280">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M280">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N280">
         <v>1</v>
@@ -15123,16 +15123,16 @@
         <v>4</v>
       </c>
       <c r="J281">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K281">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L281">
         <v>2</v>
       </c>
       <c r="M281">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N281">
         <v>3</v>
@@ -15176,7 +15176,7 @@
         <v>5</v>
       </c>
       <c r="L282">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M282">
         <v>6</v>
@@ -15217,19 +15217,19 @@
         <v>7</v>
       </c>
       <c r="J283">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K283">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L283">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M283">
         <v>3</v>
       </c>
       <c r="N283">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O283">
         <v>6</v>
@@ -15264,7 +15264,7 @@
         <v>7</v>
       </c>
       <c r="J284">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K284">
         <v>3</v>
@@ -15320,7 +15320,7 @@
         <v>1</v>
       </c>
       <c r="M285">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N285">
         <v>1</v>
@@ -15414,7 +15414,7 @@
         <v>2</v>
       </c>
       <c r="M287">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N287">
         <v>4</v>
@@ -15452,13 +15452,13 @@
         <v>3</v>
       </c>
       <c r="J288">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K288">
         <v>2</v>
       </c>
       <c r="L288">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M288">
         <v>2</v>
@@ -15546,16 +15546,16 @@
         <v>3</v>
       </c>
       <c r="J290">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K290">
         <v>4</v>
       </c>
       <c r="L290">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M290">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N290">
         <v>6</v>
@@ -15602,10 +15602,10 @@
         <v>4</v>
       </c>
       <c r="M291">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N291">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O291">
         <v>6</v>
@@ -15734,19 +15734,19 @@
         <v>6</v>
       </c>
       <c r="J294">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K294">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L294">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M294">
         <v>4</v>
       </c>
       <c r="N294">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O294">
         <v>6</v>
@@ -15781,7 +15781,7 @@
         <v>3</v>
       </c>
       <c r="J295">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K295">
         <v>1</v>
@@ -15790,10 +15790,10 @@
         <v>2</v>
       </c>
       <c r="M295">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N295">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O295">
         <v>6</v>
@@ -15831,7 +15831,7 @@
         <v>4</v>
       </c>
       <c r="K296">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L296">
         <v>3</v>
@@ -15887,7 +15887,7 @@
         <v>3</v>
       </c>
       <c r="N297">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O297">
         <v>6</v>
@@ -15922,7 +15922,7 @@
         <v>4</v>
       </c>
       <c r="J298">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K298">
         <v>2</v>
@@ -15969,19 +15969,19 @@
         <v>7</v>
       </c>
       <c r="J299">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K299">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L299">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M299">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N299">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O299">
         <v>6</v>
@@ -16066,7 +16066,7 @@
         <v>6</v>
       </c>
       <c r="K301">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L301">
         <v>6</v>
@@ -16119,7 +16119,7 @@
         <v>1</v>
       </c>
       <c r="M302">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N302">
         <v>1</v>
@@ -16204,7 +16204,7 @@
         <v>3</v>
       </c>
       <c r="J304">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K304">
         <v>1</v>
@@ -16257,13 +16257,13 @@
         <v>4</v>
       </c>
       <c r="L305">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M305">
         <v>6</v>
       </c>
       <c r="N305">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O305">
         <v>6</v>
@@ -16298,19 +16298,19 @@
         <v>2</v>
       </c>
       <c r="J306">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K306">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L306">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M306">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N306">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O306">
         <v>6</v>
@@ -16348,13 +16348,13 @@
         <v>3</v>
       </c>
       <c r="K307">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L307">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M307">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N307">
         <v>2</v>
@@ -16392,19 +16392,19 @@
         <v>5</v>
       </c>
       <c r="J308">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K308">
         <v>4</v>
       </c>
       <c r="L308">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M308">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N308">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O308">
         <v>6</v>
@@ -16533,19 +16533,19 @@
         <v>3</v>
       </c>
       <c r="J311">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K311">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L311">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M311">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N311">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O311">
         <v>6</v>
@@ -16583,7 +16583,7 @@
         <v>2</v>
       </c>
       <c r="K312">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L312">
         <v>2</v>
@@ -16592,7 +16592,7 @@
         <v>3</v>
       </c>
       <c r="N312">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O312">
         <v>6</v>
@@ -16627,19 +16627,19 @@
         <v>3</v>
       </c>
       <c r="J313">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K313">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L313">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M313">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N313">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O313">
         <v>6</v>
@@ -16677,16 +16677,16 @@
         <v>4</v>
       </c>
       <c r="K314">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L314">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M314">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N314">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O314">
         <v>6</v>
@@ -16721,19 +16721,19 @@
         <v>5</v>
       </c>
       <c r="J315">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K315">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L315">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M315">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N315">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O315">
         <v>6</v>
@@ -16768,19 +16768,19 @@
         <v>7</v>
       </c>
       <c r="J316">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K316">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L316">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M316">
         <v>2</v>
       </c>
       <c r="N316">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O316">
         <v>6</v>
@@ -16865,16 +16865,16 @@
         <v>2</v>
       </c>
       <c r="K318">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L318">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M318">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N318">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O318">
         <v>6</v>
@@ -16909,19 +16909,19 @@
         <v>3</v>
       </c>
       <c r="J319">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K319">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L319">
         <v>4</v>
       </c>
       <c r="M319">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N319">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O319">
         <v>6</v>
@@ -16956,19 +16956,19 @@
         <v>6</v>
       </c>
       <c r="J320">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K320">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L320">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M320">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N320">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O320">
         <v>6</v>
@@ -17003,19 +17003,19 @@
         <v>6</v>
       </c>
       <c r="J321">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K321">
         <v>3</v>
       </c>
       <c r="L321">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M321">
         <v>4</v>
       </c>
       <c r="N321">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O321">
         <v>6</v>
@@ -17053,16 +17053,16 @@
         <v>2</v>
       </c>
       <c r="K322">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L322">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M322">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N322">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O322">
         <v>6</v>
@@ -17100,7 +17100,7 @@
         <v>3</v>
       </c>
       <c r="K323">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L323">
         <v>3</v>
@@ -17144,19 +17144,19 @@
         <v>4</v>
       </c>
       <c r="J324">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K324">
         <v>3</v>
       </c>
       <c r="L324">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M324">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N324">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O324">
         <v>6</v>
@@ -17238,7 +17238,7 @@
         <v>5</v>
       </c>
       <c r="J326">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K326">
         <v>4</v>
@@ -17335,13 +17335,13 @@
         <v>2</v>
       </c>
       <c r="K328">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L328">
         <v>3</v>
       </c>
       <c r="M328">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N328">
         <v>2</v>
@@ -17388,10 +17388,10 @@
         <v>4</v>
       </c>
       <c r="M329">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N329">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O329">
         <v>6</v>
@@ -17426,13 +17426,13 @@
         <v>6</v>
       </c>
       <c r="J330">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K330">
         <v>4</v>
       </c>
       <c r="L330">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M330">
         <v>3</v>
@@ -17473,19 +17473,19 @@
         <v>6</v>
       </c>
       <c r="J331">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K331">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L331">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M331">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N331">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O331">
         <v>6</v>
@@ -17567,19 +17567,19 @@
         <v>6</v>
       </c>
       <c r="J333">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K333">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L333">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M333">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N333">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O333">
         <v>6</v>
@@ -17617,13 +17617,13 @@
         <v>4</v>
       </c>
       <c r="K334">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L334">
         <v>4</v>
       </c>
       <c r="M334">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N334">
         <v>4</v>
@@ -17664,16 +17664,16 @@
         <v>1</v>
       </c>
       <c r="K335">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L335">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M335">
         <v>1</v>
       </c>
       <c r="N335">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O335">
         <v>6</v>
@@ -17943,19 +17943,19 @@
         <v>3</v>
       </c>
       <c r="J341">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K341">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L341">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M341">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N341">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O341">
         <v>6</v>
@@ -18037,19 +18037,19 @@
         <v>4</v>
       </c>
       <c r="J343">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K343">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L343">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M343">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N343">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O343">
         <v>6</v>
@@ -18131,7 +18131,7 @@
         <v>6</v>
       </c>
       <c r="J345">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K345">
         <v>2</v>
@@ -18143,7 +18143,7 @@
         <v>5</v>
       </c>
       <c r="N345">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O345">
         <v>6</v>
@@ -18178,16 +18178,16 @@
         <v>4</v>
       </c>
       <c r="J346">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K346">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L346">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M346">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N346">
         <v>1</v>
@@ -18231,13 +18231,13 @@
         <v>2</v>
       </c>
       <c r="L347">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M347">
         <v>3</v>
       </c>
       <c r="N347">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O347">
         <v>6</v>
@@ -18272,19 +18272,19 @@
         <v>7</v>
       </c>
       <c r="J348">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K348">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L348">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M348">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N348">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O348">
         <v>6</v>
@@ -18319,16 +18319,16 @@
         <v>4</v>
       </c>
       <c r="J349">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K349">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L349">
         <v>4</v>
       </c>
       <c r="M349">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N349">
         <v>4</v>
@@ -18366,19 +18366,19 @@
         <v>6</v>
       </c>
       <c r="J350">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K350">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L350">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M350">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N350">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O350">
         <v>6</v>
@@ -18413,7 +18413,7 @@
         <v>5</v>
       </c>
       <c r="J351">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K351">
         <v>2</v>
@@ -18507,19 +18507,19 @@
         <v>6</v>
       </c>
       <c r="J353">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K353">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L353">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M353">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N353">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O353">
         <v>6</v>
@@ -18554,19 +18554,19 @@
         <v>3</v>
       </c>
       <c r="J354">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K354">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L354">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M354">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N354">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O354">
         <v>6</v>
@@ -18651,7 +18651,7 @@
         <v>3</v>
       </c>
       <c r="K356">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L356">
         <v>4</v>
@@ -18742,19 +18742,19 @@
         <v>5</v>
       </c>
       <c r="J358">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K358">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L358">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M358">
         <v>2</v>
       </c>
       <c r="N358">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O358">
         <v>6</v>
@@ -18842,7 +18842,7 @@
         <v>4</v>
       </c>
       <c r="L360">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M360">
         <v>4</v>
@@ -18930,19 +18930,19 @@
         <v>3</v>
       </c>
       <c r="J362">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K362">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L362">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M362">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N362">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O362">
         <v>6</v>
@@ -18977,10 +18977,10 @@
         <v>5</v>
       </c>
       <c r="J363">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K363">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L363">
         <v>5</v>
@@ -19033,7 +19033,7 @@
         <v>4</v>
       </c>
       <c r="M364">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N364">
         <v>4</v>
@@ -19074,13 +19074,13 @@
         <v>2</v>
       </c>
       <c r="K365">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L365">
         <v>2</v>
       </c>
       <c r="M365">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N365">
         <v>1</v>
@@ -19177,7 +19177,7 @@
         <v>4</v>
       </c>
       <c r="N367">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O367">
         <v>6</v>
@@ -19221,7 +19221,7 @@
         <v>4</v>
       </c>
       <c r="M368">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N368">
         <v>4</v>
@@ -19306,19 +19306,19 @@
         <v>7</v>
       </c>
       <c r="J370">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K370">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L370">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M370">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N370">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O370">
         <v>6</v>
@@ -19353,13 +19353,13 @@
         <v>5</v>
       </c>
       <c r="J371">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K371">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L371">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M371">
         <v>3</v>
@@ -19400,19 +19400,19 @@
         <v>4</v>
       </c>
       <c r="J372">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K372">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L372">
         <v>4</v>
       </c>
       <c r="M372">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N372">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O372">
         <v>6</v>
@@ -19459,7 +19459,7 @@
         <v>3</v>
       </c>
       <c r="N373">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O373">
         <v>6</v>
@@ -19494,7 +19494,7 @@
         <v>6</v>
       </c>
       <c r="J374">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K374">
         <v>5</v>
@@ -19503,7 +19503,7 @@
         <v>5</v>
       </c>
       <c r="M374">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N374">
         <v>5</v>
@@ -19544,13 +19544,13 @@
         <v>3</v>
       </c>
       <c r="K375">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L375">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M375">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N375">
         <v>3</v>
@@ -19635,7 +19635,7 @@
         <v>3</v>
       </c>
       <c r="J377">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K377">
         <v>4</v>
@@ -19644,10 +19644,10 @@
         <v>3</v>
       </c>
       <c r="M377">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N377">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O377">
         <v>6</v>
@@ -19688,7 +19688,7 @@
         <v>1</v>
       </c>
       <c r="L378">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M378">
         <v>3</v>
@@ -19729,19 +19729,19 @@
         <v>5</v>
       </c>
       <c r="J379">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K379">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L379">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M379">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N379">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O379">
         <v>6</v>
@@ -19776,19 +19776,19 @@
         <v>5</v>
       </c>
       <c r="J380">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K380">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L380">
         <v>2</v>
       </c>
       <c r="M380">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N380">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O380">
         <v>6</v>
@@ -19823,19 +19823,19 @@
         <v>6</v>
       </c>
       <c r="J381">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K381">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L381">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M381">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N381">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O381">
         <v>6</v>
@@ -19870,19 +19870,19 @@
         <v>6</v>
       </c>
       <c r="J382">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K382">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L382">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M382">
         <v>3</v>
       </c>
       <c r="N382">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O382">
         <v>6</v>
@@ -19917,19 +19917,19 @@
         <v>4</v>
       </c>
       <c r="J383">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K383">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L383">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M383">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N383">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O383">
         <v>6</v>
@@ -20014,16 +20014,16 @@
         <v>1</v>
       </c>
       <c r="K385">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L385">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M385">
         <v>2</v>
       </c>
       <c r="N385">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O385">
         <v>6</v>
@@ -20152,16 +20152,16 @@
         <v>4</v>
       </c>
       <c r="J388">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K388">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L388">
         <v>3</v>
       </c>
       <c r="M388">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N388">
         <v>3</v>
@@ -20246,7 +20246,7 @@
         <v>4</v>
       </c>
       <c r="J390">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K390">
         <v>4</v>
@@ -20255,7 +20255,7 @@
         <v>4</v>
       </c>
       <c r="M390">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N390">
         <v>4</v>
@@ -20293,19 +20293,19 @@
         <v>4</v>
       </c>
       <c r="J391">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K391">
         <v>4</v>
       </c>
       <c r="L391">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M391">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N391">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O391">
         <v>6</v>
@@ -20346,10 +20346,10 @@
         <v>3</v>
       </c>
       <c r="L392">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M392">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N392">
         <v>1</v>
@@ -20387,19 +20387,19 @@
         <v>4</v>
       </c>
       <c r="J393">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K393">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L393">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M393">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N393">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O393">
         <v>6</v>
@@ -20487,7 +20487,7 @@
         <v>2</v>
       </c>
       <c r="L395">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M395">
         <v>2</v>
@@ -20575,19 +20575,19 @@
         <v>3</v>
       </c>
       <c r="J397">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K397">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L397">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M397">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N397">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O397">
         <v>6</v>
@@ -20716,19 +20716,19 @@
         <v>6</v>
       </c>
       <c r="J400">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K400">
         <v>5</v>
       </c>
       <c r="L400">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M400">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N400">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O400">
         <v>6</v>
@@ -20857,16 +20857,16 @@
         <v>4</v>
       </c>
       <c r="J403">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K403">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L403">
         <v>4</v>
       </c>
       <c r="M403">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N403">
         <v>3</v>
@@ -20916,7 +20916,7 @@
         <v>3</v>
       </c>
       <c r="N404">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O404">
         <v>6</v>
@@ -20998,19 +20998,19 @@
         <v>6</v>
       </c>
       <c r="J406">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K406">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L406">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M406">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N406">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O406">
         <v>6</v>
@@ -21057,7 +21057,7 @@
         <v>3</v>
       </c>
       <c r="N407">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O407">
         <v>6</v>
@@ -21095,10 +21095,10 @@
         <v>3</v>
       </c>
       <c r="K408">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L408">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M408">
         <v>2</v>
@@ -21139,19 +21139,19 @@
         <v>7</v>
       </c>
       <c r="J409">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K409">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L409">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M409">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N409">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O409">
         <v>6</v>
@@ -21186,19 +21186,19 @@
         <v>4</v>
       </c>
       <c r="J410">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K410">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L410">
         <v>3</v>
       </c>
       <c r="M410">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N410">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O410">
         <v>6</v>
@@ -21280,13 +21280,13 @@
         <v>5</v>
       </c>
       <c r="J412">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K412">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L412">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M412">
         <v>2</v>
@@ -21374,13 +21374,13 @@
         <v>5</v>
       </c>
       <c r="J414">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K414">
         <v>2</v>
       </c>
       <c r="L414">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M414">
         <v>4</v>
@@ -21424,13 +21424,13 @@
         <v>5</v>
       </c>
       <c r="K415">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L415">
         <v>5</v>
       </c>
       <c r="M415">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N415">
         <v>5</v>
@@ -21518,13 +21518,13 @@
         <v>3</v>
       </c>
       <c r="K417">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L417">
         <v>2</v>
       </c>
       <c r="M417">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N417">
         <v>1</v>
@@ -21571,7 +21571,7 @@
         <v>1</v>
       </c>
       <c r="M418">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N418">
         <v>1</v>
@@ -21612,16 +21612,16 @@
         <v>3</v>
       </c>
       <c r="K419">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L419">
         <v>3</v>
       </c>
       <c r="M419">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N419">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O419">
         <v>6</v>
@@ -21703,7 +21703,7 @@
         <v>4</v>
       </c>
       <c r="J421">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K421">
         <v>5</v>
